--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C00C1A-79BA-4CD7-9E25-78200483B2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8563B-E12A-4475-9950-B9437299B2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="604">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -2067,6 +2067,15 @@
   </si>
   <si>
     <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-10-07-2024-354-pro-zatverdzhennya-rekomendacii-z-ocinki-dostatnosti-zakhodiv-zakhistu-informaciyi-kompleksnikh-sistem-zakhistu-informaciyi-v-informaciinikh-elektronnikh-komunikaciinikh-ta-informaciino-komunikaciinikh-sistemakh-stvorenikh-z-vikoristannyam-profiliv-bezpeki-informaciyi</t>
+  </si>
+  <si>
+    <t>https://ips.ligazakon.net/document/re46274</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 02.06.2026 № 402</t>
+  </si>
+  <si>
+    <t>Ця Методика встановлює єдиний підхід до ідентифікації та оцінювання ризиків кібербезпеки для органів державної влади, інших державних органів, органів місцевого самоврядування, державних підприємств, установ та організацій, які є власниками або розпорядниками інформаційних, електронних комунікаційних, інформаційно-комунікаційних та технологічних систем (далі - системи), в яких обробляються державні інформаційні ресурси (далі - ДІР) або інформація з обмеженим доступом, вимога щодо захисту якої встановлена законом (далі - ІзОД), операторами критичної інфраструктури та власниками або розпорядниками об'єктів критичної інформаційної інфраструктури (далі - ОКII) та застосовується під час формування поточного та/або цільового станів кіберзахисту, розроблення планів кіберзахисту.</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2303,29 +2312,20 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="25">
     <dxf>
       <font>
         <b/>
@@ -2823,13 +2823,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -2857,6 +2850,13 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2894,51 +2894,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2953,7 +2908,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J243" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowBorderDxfId="21" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J243" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21">
   <autoFilter ref="B18:J243" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
     <sortCondition ref="B18:B200"/>
@@ -3270,7 +3225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J244"/>
+  <dimension ref="A2:J245"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3287,14 +3242,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -9332,49 +9287,73 @@
         <v>508</v>
       </c>
     </row>
-    <row r="243" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B243" s="25">
+    <row r="243" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="B243" s="7">
         <v>225</v>
       </c>
-      <c r="C243" s="25" t="s">
+      <c r="C243" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="D243" s="25" t="s">
+      <c r="D243" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="E243" s="25"/>
-      <c r="F243" s="25" t="s">
+      <c r="E243" s="7"/>
+      <c r="F243" s="7" t="s">
         <v>197</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H243" s="25"/>
-      <c r="I243" s="27">
+      <c r="H243" s="7"/>
+      <c r="I243" s="14">
         <v>45483</v>
       </c>
-      <c r="J243" s="26"/>
+      <c r="J243" s="15"/>
     </row>
     <row r="244" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B244" s="28">
+      <c r="B244" s="24">
         <v>226</v>
       </c>
-      <c r="C244" s="28" t="s">
+      <c r="C244" s="24" t="s">
         <v>599</v>
       </c>
-      <c r="D244" s="28" t="s">
+      <c r="D244" s="24" t="s">
         <v>598</v>
       </c>
-      <c r="E244" s="28"/>
-      <c r="F244" s="28" t="s">
+      <c r="E244" s="24"/>
+      <c r="F244" s="24" t="s">
         <v>197</v>
       </c>
       <c r="G244" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H244" s="28"/>
-      <c r="I244" s="29">
+      <c r="H244" s="24"/>
+      <c r="I244" s="25">
         <v>45467</v>
+      </c>
+    </row>
+    <row r="245" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="B245" s="24">
+        <v>227</v>
+      </c>
+      <c r="C245" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="D245" s="24" t="s">
+        <v>601</v>
+      </c>
+      <c r="E245" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="F245" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H245" s="24"/>
+      <c r="I245" s="25">
+        <v>46175</v>
       </c>
     </row>
   </sheetData>
@@ -9384,7 +9363,7 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G244">
+  <conditionalFormatting sqref="G19:G245">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>

--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8563B-E12A-4475-9950-B9437299B2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E48ED9-4905-4EBE-AEF0-CA8BF156B336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="610">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -2069,13 +2069,33 @@
     <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-10-07-2024-354-pro-zatverdzhennya-rekomendacii-z-ocinki-dostatnosti-zakhodiv-zakhistu-informaciyi-kompleksnikh-sistem-zakhistu-informaciyi-v-informaciinikh-elektronnikh-komunikaciinikh-ta-informaciino-komunikaciinikh-sistemakh-stvorenikh-z-vikoristannyam-profiliv-bezpeki-informaciyi</t>
   </si>
   <si>
-    <t>https://ips.ligazakon.net/document/re46274</t>
-  </si>
-  <si>
-    <t>Наказ Адміністрації Держспецзв’язку від 02.06.2026 № 402</t>
-  </si>
-  <si>
     <t>Ця Методика встановлює єдиний підхід до ідентифікації та оцінювання ризиків кібербезпеки для органів державної влади, інших державних органів, органів місцевого самоврядування, державних підприємств, установ та організацій, які є власниками або розпорядниками інформаційних, електронних комунікаційних, інформаційно-комунікаційних та технологічних систем (далі - системи), в яких обробляються державні інформаційні ресурси (далі - ДІР) або інформація з обмеженим доступом, вимога щодо захисту якої встановлена законом (далі - ІзОД), операторами критичної інфраструктури та власниками або розпорядниками об'єктів критичної інформаційної інфраструктури (далі - ОКII) та застосовується під час формування поточного та/або цільового станів кіберзахисту, розроблення планів кіберзахисту.</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 08 червня 2026 року № 425 «Про затвердження Порядку взаємодії галузевих та регіональних команд реагування на кіберінциденти, кібератаки, кіберзагрози (CSIRT) з національною командою реагування на кіберінциденти, кібератаки, кіберзагрози (CERT-UA) та приватних команд реагування на кіберінциденти, кібератаки, кіберзагрози з іншими суб’єктами національної системи реагування на кіберінциденти, кібератаки, кіберзагрози», зареєстрований у Мін’юсті 30 червня 2026 р. за № 954/46348;</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0954-26#Text</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 04 червня 2026 року № 410 «Про затвердження Порядку приєднання суб’єктів забезпечення кібербезпеки до платформи обміну інформацією про кіберінциденти, кібератаки, кіберзагрози», зареєстрований у Мін’юсті 22 червня 2026 р. за № 898/46292</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0898-26#Text</t>
+  </si>
+  <si>
+    <t>Цей Порядок визначає механізм та умови приєднання основних суб’єктів національної системи кібербезпеки, суб’єктів національної системи реагування, органів державної влади, державних органів, органів місцевого самоврядування, операторів критичної інфраструктури, власників або розпорядників об’єктів критичної інформаційної інфраструктури, інших суб’єктів забезпечення кібербезпеки, які відповідно до законодавства залучені до виконання завдань в рамках функціонування національної системи реагування, до платформи обміну інформацією про кіберінциденти, кібератаки, кіберзагрози</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0880-26</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв’язку від 02.06.2026 № 402 "Про затвердження Методики оцінювання ризиків кібербезпеки"</t>
+  </si>
+  <si>
+    <t>Цей Порядок визначає механізм взаємодії:
+галузевих та регіональних команд реагування на кіберінциденти, кібератаки, кіберзагрози з національною командою реагування на кіберінциденти, кібератаки, кіберзагрози;
+приватних команд реагування на кіберінциденти, кібератаки, кіберзагрози з іншими суб’єктами національної системи реагування на кіберінциденти, кібератаки, кіберзагрози.</t>
   </si>
 </sst>
 </file>
@@ -3225,7 +3245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J245"/>
+  <dimension ref="A2:J247"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -9337,13 +9357,13 @@
         <v>227</v>
       </c>
       <c r="C245" s="24" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="D245" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="E245" s="24" t="s">
         <v>601</v>
-      </c>
-      <c r="E245" s="24" t="s">
-        <v>603</v>
       </c>
       <c r="F245" s="24" t="s">
         <v>197</v>
@@ -9354,6 +9374,54 @@
       <c r="H245" s="24"/>
       <c r="I245" s="25">
         <v>46175</v>
+      </c>
+    </row>
+    <row r="246" spans="2:10" ht="248.4" x14ac:dyDescent="0.25">
+      <c r="B246" s="24">
+        <v>228</v>
+      </c>
+      <c r="C246" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="D246" s="24" t="s">
+        <v>603</v>
+      </c>
+      <c r="E246" s="24" t="s">
+        <v>609</v>
+      </c>
+      <c r="F246" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H246" s="24"/>
+      <c r="I246" s="25">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="247" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B247" s="24">
+        <v>229</v>
+      </c>
+      <c r="C247" s="24" t="s">
+        <v>604</v>
+      </c>
+      <c r="D247" s="24" t="s">
+        <v>605</v>
+      </c>
+      <c r="E247" s="24" t="s">
+        <v>606</v>
+      </c>
+      <c r="F247" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H247" s="24"/>
+      <c r="I247" s="25">
+        <v>46177</v>
       </c>
     </row>
   </sheetData>
@@ -9363,7 +9431,7 @@
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G245">
+  <conditionalFormatting sqref="G19:G247">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>

--- a/Застосовне законодавство.xlsx
+++ b/Застосовне законодавство.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\користувач\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E48ED9-4905-4EBE-AEF0-CA8BF156B336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B604DE-6F47-44C6-A31D-23B61039E313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{334805C5-B449-4CB8-AF80-1835CA06DE69}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="612">
   <si>
     <t>- В цьому реєстрі перераховані тільки основні законодавчі акти, не враховуючи супутні акти, що затверджують зміни, або покладають завдання з реалізації, наприклад, Національної стратегії кібербезпеки.
 - Сайт ВРУ - основне джерело інформації, оскільки на ньому можна відстежувати актуальність законодавчих актів.</t>
@@ -1030,9 +1030,6 @@
     <t>НД ТЗІ 2.7-012-2015</t>
   </si>
   <si>
-    <t>НД ТЗІ 3.6-001-2000 "Технічний захист інформації. Комп’ютерні системи. Порядок створення, впровадження, супро­водження та модернізації засобів технічного захисту інформації від несанкціонованого доступу"</t>
-  </si>
-  <si>
     <t>НД ТЗІ 3.6-003-2016 "Порядок проведення робіт зі створення та атестації комплексів технічного захисту інформації"</t>
   </si>
   <si>
@@ -1113,9 +1110,6 @@
   </si>
   <si>
     <t>https://cip.gov.ua/services/cm/api/attachment/download?id=65232</t>
-  </si>
-  <si>
-    <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-30-04-2024-228-pro-zatverdzhennya-vimog-do-auditoriv-informaciinoyi-bezpeki-na-ob-yektakh-kritichnoyi-infrastrukturi-ta-poryadku-yikh-atestaciyi-pereatestaciyi</t>
   </si>
   <si>
     <t>Наказ Адміністрації Держспецзв’язку від 30.04.2024 № 228 «Про затвердження Вимог до аудиторів інформаційної безпеки на об’єктах критичної інфраструктури та порядку їх атестації (переатестації)»</t>
@@ -1380,12 +1374,6 @@
     <t>Наказ Адміністрації Держспецзв’язку від 27.11.2024 № 702 «Про затвердження Методичних рекомендацій щодо проведення незалежного аудиту інформаційної безпеки на об’єктах критичної інфраструктури»</t>
   </si>
   <si>
-    <t>https://www.kmu.gov.ua/npas/deiaki-pytannia-stvorennia-administruvannia-ta-zabezpechennia-funktsionuvannia-zasobu-t210225</t>
-  </si>
-  <si>
-    <t>https://www.kmu.gov.ua/npas/deiaki-pytannia-nadannia-ta-vykorystannia-khmarnykh-posluh-taabo-posluh-tsentru-obrobky-danykh-154-110225</t>
-  </si>
-  <si>
     <t>Постанова Кабінету Міністрів України від 21 лютого 2025 р. № 205 "Деякі питання створення, адміністрування та забезпечення функціонування засобу інформатизації"</t>
   </si>
   <si>
@@ -1501,9 +1489,6 @@
   </si>
   <si>
     <t>Постанова Кабінету Міністрів України від 18.06.2025 № 712 "Деякі питання захисту інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем"</t>
-  </si>
-  <si>
-    <t>https://www.kmu.gov.ua/npas/pro-zatverdzhennia-poriadku-provedennia-instruktazhiv-ta-systematychnykh-treninhiv-s1281081025</t>
   </si>
   <si>
     <t>Постанова Кабінету Міністрів України від 08 жовтня 2025 р. №1281 "Про затвердження Порядку проведення інструктажів та систематичних тренінгів щодо кібергігієни"</t>
@@ -1843,15 +1828,6 @@
   </si>
   <si>
     <t>Наказ Адміністрації Держспецзв’язку від 19 грудня 2025 року № 847 зареєстровано у Міністерстві юстиції України 5 січня 2026 року за № 8/45402 "Про затвердження Порядку здійснення моніторингу авторизації з безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем"</t>
-  </si>
-  <si>
-    <t>https://zakon.rada.gov.ua/laws/show/712-2025-%D0%BF#n18</t>
-  </si>
-  <si>
-    <t>Постанова Кабінету Міністрів України від 18.06.2025 № 712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цей Порядок визначає процедури проведення авторизації з безпеки інформаційних, електронних комунікаційних, інформаційно-комунікаційних, технологічних систем, в яких обробляються державні інформаційні ресурси або інформація з обмеженим доступом, вимога щодо захисту якої встановлена законом, об’єктів критичної інформаційної інфраструктури, власниками або розпорядниками яких є органи державної влади, інші державні органи, державні підприємства, установи та організації, органи місцевого самоврядування (далі - системи), а також підтвердження дотримання вимог з безпеки щодо таких систем протягом їх життєвого циклу. </t>
   </si>
   <si>
     <t>Наказ Адміністрації Держспецзв’язку від 16.04.2026 № 285 «Деякі питання проведення оцінювання стану кіберзахисту»</t>
@@ -2060,12 +2036,6 @@
     <t>Наказ Адміністрації Держспецзв’язку від 10.07.2024 №354</t>
   </si>
   <si>
-    <t>https://zakon.rada.gov.ua/rada/show/v0317519-24#Text</t>
-  </si>
-  <si>
-    <t>Наказ Адміністрації Держспецзв’язку від 24.06.2024 № 317</t>
-  </si>
-  <si>
     <t>https://cip.gov.ua/ua/news/nakaz-administraciyi-derzhspeczv-yazku-vid-10-07-2024-354-pro-zatverdzhennya-rekomendacii-z-ocinki-dostatnosti-zakhodiv-zakhistu-informaciyi-kompleksnikh-sistem-zakhistu-informaciyi-v-informaciinikh-elektronnikh-komunikaciinikh-ta-informaciino-komunikaciinikh-sistemakh-stvorenikh-z-vikoristannyam-profiliv-bezpeki-informaciyi</t>
   </si>
   <si>
@@ -2096,6 +2066,46 @@
     <t>Цей Порядок визначає механізм взаємодії:
 галузевих та регіональних команд реагування на кіберінциденти, кібератаки, кіберзагрози з національною командою реагування на кіберінциденти, кібератаки, кіберзагрози;
 приватних команд реагування на кіберінциденти, кібератаки, кіберзагрози з іншими суб’єктами національної системи реагування на кіберінциденти, кібератаки, кіберзагрози.</t>
+  </si>
+  <si>
+    <t>Дата юстування</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/119-2024-%D0%BF</t>
+  </si>
+  <si>
+    <t>Постанова Кабінету Міністрів України від 2 лютого 2024 р. № 119 “Деякі питання Національної програми інформатизації"</t>
+  </si>
+  <si>
+    <t>Положення про формування та виконання Національної програми інформатизації;
+Порядок проведення експертизи Національної програми інформатизації та її складових;
+Порядок формування та виконання галузевої програми, проекту, робіт з інформатизації;
+Порядок формування та виконання регіональної програми, проекту, робіт з інформатизації;
+Порядок здійснення моніторингу та проведення оцінки результативності виконання Національної програми інформатизації та її складових.</t>
+  </si>
+  <si>
+    <t>https://ips.ligazakon.net/document/re46528?an=10</t>
+  </si>
+  <si>
+    <t>Наказ Адміністрації Держспецзв'язку N 534 від 14 липня 2026 року "Про затвердження Вимог до суб'єктів оцінювання стану кіберзахисту"(Зареєстровано в Міністерстві юстиції України 12 серпня 2026 р. за N 1134/46528)</t>
+  </si>
+  <si>
+    <t>Вимоги містять сукупність кваліфікаційних та інших обов'язкових умов і критеріїв, яким повинні відповідати юридичні особи, фізичні особи - підприємці або фізичні особи, що проводять оцінювання стану кіберзахисту.</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/z0880-24#Text</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/205-2025-%D0%BF#Text</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/154-2025-%D0%BF#Text</t>
+  </si>
+  <si>
+    <t>https://zakon.rada.gov.ua/laws/show/1281-2025-%D0%BF#Text</t>
+  </si>
+  <si>
+    <t>і</t>
   </si>
 </sst>
 </file>
@@ -2157,7 +2167,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2178,12 +2188,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2195,7 +2199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2244,26 +2248,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2287,9 +2276,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2308,44 +2294,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
     <dxf>
       <font>
         <b/>
@@ -2480,6 +2466,26 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2928,21 +2934,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:J243" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21">
-  <autoFilter ref="B18:J243" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:I200">
-    <sortCondition ref="B18:B200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}" name="Таблиця2" displayName="Таблиця2" ref="B18:K246" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22">
+  <autoFilter ref="B18:K246" xr:uid="{FE4F2F92-58E2-48B9-A7D4-627EBB6ED48E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B19:K245">
+    <sortCondition ref="B18:B245"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="12"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DFA9E46C-509D-4A00-A369-7966EED6B176}" name="№" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{981014D8-EFBF-47F5-B054-36010B7987AF}" name="Джерело вимог" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{928FBB84-B24F-469A-AFD2-7EA49120BF89}" name="Посилання" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{D49602E6-E651-4C6D-8A88-C8DCD8A3AFDD}" name="Коментар" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{52AE3B44-6A02-4F51-99B9-C7E17C080BEC}" name="Категорія" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{DE39899F-E232-40DC-A0D1-10B3A973A842}" name="Застосовність" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{40F3EA47-8E92-48F7-A24A-6369E84EA096}" name="Теги" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{A1D4F9E4-94BB-4008-834E-B5DC4DE59C40}" name="Дата прийняття" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{2B27F073-AE91-4210-B0D6-642DEFE05F63}" name="Галузь" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{E66FA609-1D37-4BBA-B953-1F3C9DD9DBC5}" name="Дата юстування" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3245,31 +3252,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B971BF4-F5CF-496D-9610-E7CBA5A28B9C}">
-  <dimension ref="A2:J247"/>
+  <dimension ref="A2:K246"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="5.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="48.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="62.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.77734375" style="1" customWidth="1"/>
     <col min="10" max="10" width="27.109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="10.21875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -3330,7 +3338,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -3342,12 +3350,12 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="17" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3362,8 +3370,8 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="21" t="s">
-        <v>578</v>
+      <c r="H10" s="17" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3387,13 +3395,13 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="20" t="s">
-        <v>577</v>
+      <c r="H12" s="16" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3407,17 +3415,17 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="23" t="s">
-        <v>579</v>
+      <c r="H13" s="18" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -3427,10 +3435,10 @@
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E15" s="2"/>
       <c r="G15" s="2"/>
@@ -3440,17 +3448,17 @@
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3460,7 +3468,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
       <c r="B18" s="5" t="s">
         <v>12</v>
@@ -3483,14 +3491,17 @@
       <c r="H18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="189.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="189.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="6">
         <v>1</v>
@@ -3511,12 +3522,13 @@
         <v>10</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="I19" s="11"/>
+      <c r="J19" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="6">
         <v>2</v>
@@ -3539,10 +3551,11 @@
       <c r="H20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="6">
         <v>3</v>
@@ -3563,10 +3576,11 @@
         <v>10</v>
       </c>
       <c r="H21" s="6"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="6">
         <v>4</v>
@@ -3587,10 +3601,11 @@
         <v>10</v>
       </c>
       <c r="H22" s="6"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="6">
         <v>5</v>
@@ -3611,10 +3626,11 @@
         <v>10</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="6">
         <v>6</v>
@@ -3635,10 +3651,11 @@
         <v>10</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="6">
         <v>7</v>
@@ -3659,10 +3676,11 @@
         <v>10</v>
       </c>
       <c r="H25" s="6"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-    </row>
-    <row r="26" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="6">
         <v>8</v>
@@ -3671,10 +3689,10 @@
         <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>22</v>
@@ -3683,10 +3701,11 @@
         <v>10</v>
       </c>
       <c r="H26" s="6"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="6">
         <v>9</v>
@@ -3695,10 +3714,10 @@
         <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>22</v>
@@ -3707,10 +3726,11 @@
         <v>10</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="6">
         <v>10</v>
@@ -3719,7 +3739,7 @@
         <v>46</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>44</v>
@@ -3731,10 +3751,11 @@
         <v>10</v>
       </c>
       <c r="H28" s="6"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="6">
         <v>11</v>
@@ -3757,10 +3778,11 @@
       <c r="H29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="6">
         <v>12</v>
@@ -3769,10 +3791,10 @@
         <v>51</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>22</v>
@@ -3781,10 +3803,11 @@
         <v>10</v>
       </c>
       <c r="H30" s="6"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="6">
         <v>13</v>
@@ -3805,10 +3828,11 @@
         <v>10</v>
       </c>
       <c r="H31" s="6"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="6">
         <v>14</v>
@@ -3829,10 +3853,11 @@
         <v>10</v>
       </c>
       <c r="H32" s="6"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="6">
         <v>15</v>
@@ -3853,10 +3878,11 @@
         <v>10</v>
       </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="6">
         <v>16</v>
@@ -3865,10 +3891,10 @@
         <v>57</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>22</v>
@@ -3877,10 +3903,11 @@
         <v>10</v>
       </c>
       <c r="H34" s="6"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-    </row>
-    <row r="35" spans="1:10" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="4"/>
+    </row>
+    <row r="35" spans="1:11" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="6">
         <v>17</v>
@@ -3903,10 +3930,11 @@
       <c r="H35" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-    </row>
-    <row r="36" spans="1:10" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="6">
         <v>18</v>
@@ -3929,12 +3957,13 @@
       <c r="H36" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="10">
         <v>43013</v>
       </c>
-      <c r="J36" s="10"/>
-    </row>
-    <row r="37" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="J36" s="9"/>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="6">
         <v>19</v>
@@ -3957,12 +3986,13 @@
       <c r="H37" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="10">
         <v>43272</v>
       </c>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="J37" s="9"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="6">
         <v>20</v>
@@ -3985,12 +4015,13 @@
       <c r="H38" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="10">
         <v>38771</v>
       </c>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="J38" s="9"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="6">
         <v>21</v>
@@ -4013,14 +4044,15 @@
       <c r="H39" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="10">
         <v>44516</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="6">
         <v>22</v>
@@ -4041,14 +4073,15 @@
         <v>10</v>
       </c>
       <c r="H40" s="6"/>
-      <c r="I40" s="11">
+      <c r="I40" s="10">
         <v>44181</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="6">
         <v>23</v>
@@ -4060,7 +4093,7 @@
         <v>79</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>65</v>
@@ -4069,14 +4102,15 @@
         <v>10</v>
       </c>
       <c r="H41" s="6"/>
-      <c r="I41" s="11">
+      <c r="I41" s="10">
         <v>34520</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="6">
         <v>24</v>
@@ -4097,14 +4131,15 @@
         <v>10</v>
       </c>
       <c r="H42" s="6"/>
-      <c r="I42" s="11">
+      <c r="I42" s="10">
         <v>43013</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="6">
         <v>25</v>
@@ -4127,14 +4162,15 @@
       <c r="H43" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="10">
         <v>40330</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="6">
         <v>26</v>
@@ -4155,14 +4191,15 @@
         <v>10</v>
       </c>
       <c r="H44" s="6"/>
-      <c r="I44" s="11">
+      <c r="I44" s="10">
         <v>40556</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" spans="1:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="6">
         <v>27</v>
@@ -4185,14 +4222,15 @@
       <c r="H45" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="10">
         <v>44609</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="6">
         <v>28</v>
@@ -4215,14 +4253,15 @@
       <c r="H46" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="10">
         <v>44434</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" spans="1:11" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="6">
         <v>29</v>
@@ -4245,14 +4284,15 @@
       <c r="H47" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="10">
         <v>44593</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="6">
         <v>30</v>
@@ -4273,14 +4313,15 @@
         <v>10</v>
       </c>
       <c r="H48" s="6"/>
-      <c r="I48" s="11">
+      <c r="I48" s="10">
         <v>35937</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="6">
         <v>31</v>
@@ -4303,14 +4344,15 @@
       <c r="H49" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="10">
         <v>36430</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="6">
         <v>32</v>
@@ -4331,14 +4373,15 @@
         <v>10</v>
       </c>
       <c r="H50" s="6"/>
-      <c r="I50" s="11">
+      <c r="I50" s="10">
         <v>41885</v>
       </c>
       <c r="J50" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="6">
         <v>33</v>
@@ -4361,14 +4404,15 @@
       <c r="H51" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="10">
         <v>43635</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="6">
         <v>34</v>
@@ -4391,14 +4435,15 @@
       <c r="H52" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="10">
         <v>44113</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="6">
         <v>35</v>
@@ -4421,14 +4466,15 @@
       <c r="H53" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="10">
         <v>44113</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="6">
         <v>36</v>
@@ -4451,14 +4497,15 @@
       <c r="H54" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="10">
         <v>44146</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="6">
         <v>37</v>
@@ -4481,12 +4528,13 @@
       <c r="H55" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="10">
         <v>44188</v>
       </c>
-      <c r="J55" s="10"/>
-    </row>
-    <row r="56" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J55" s="9"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="6">
         <v>38</v>
@@ -4509,12 +4557,13 @@
       <c r="H56" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="10">
         <v>45023</v>
       </c>
-      <c r="J56" s="10"/>
-    </row>
-    <row r="57" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J56" s="9"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="6">
         <v>39</v>
@@ -4537,12 +4586,13 @@
       <c r="H57" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="10">
         <v>44559</v>
       </c>
-      <c r="J57" s="10"/>
-    </row>
-    <row r="58" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J57" s="9"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="6">
         <v>40</v>
@@ -4559,16 +4609,17 @@
       <c r="F58" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>10</v>
+      <c r="G58" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H58" s="6"/>
-      <c r="I58" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="J58" s="10"/>
-    </row>
-    <row r="59" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="I58" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="J58" s="9"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="6">
         <v>41</v>
@@ -4589,12 +4640,13 @@
         <v>10</v>
       </c>
       <c r="H59" s="6"/>
-      <c r="I59" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="J59" s="10"/>
-    </row>
-    <row r="60" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="I59" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="J59" s="9"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="6">
         <v>42</v>
@@ -4606,7 +4658,7 @@
         <v>138</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>110</v>
@@ -4615,12 +4667,13 @@
         <v>10</v>
       </c>
       <c r="H60" s="6"/>
-      <c r="I60" s="11">
+      <c r="I60" s="10">
         <v>38805</v>
       </c>
-      <c r="J60" s="10"/>
-    </row>
-    <row r="61" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J60" s="9"/>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="6">
         <v>43</v>
@@ -4643,12 +4696,13 @@
       <c r="H61" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="10">
         <v>35711</v>
       </c>
-      <c r="J61" s="10"/>
-    </row>
-    <row r="62" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J61" s="9"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="6">
         <v>44</v>
@@ -4660,23 +4714,24 @@
         <v>143</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G62" s="23" t="s">
-        <v>579</v>
+      <c r="G62" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="10">
         <v>40037</v>
       </c>
-      <c r="J62" s="10"/>
-    </row>
-    <row r="63" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J62" s="9"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="6">
         <v>45</v>
@@ -4699,12 +4754,13 @@
       <c r="H63" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="10">
         <v>37819</v>
       </c>
-      <c r="J63" s="10"/>
-    </row>
-    <row r="64" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J63" s="9"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="6">
         <v>46</v>
@@ -4721,18 +4777,19 @@
       <c r="F64" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="10">
         <v>37819</v>
       </c>
-      <c r="J64" s="10"/>
-    </row>
-    <row r="65" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J64" s="9"/>
+      <c r="K64" s="4"/>
+    </row>
+    <row r="65" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="6">
         <v>47</v>
@@ -4755,12 +4812,13 @@
       <c r="H65" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="10">
         <v>37328</v>
       </c>
-      <c r="J65" s="10"/>
-    </row>
-    <row r="66" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J65" s="9"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="6">
         <v>48</v>
@@ -4783,12 +4841,13 @@
       <c r="H66" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="10">
         <v>41626</v>
       </c>
-      <c r="J66" s="10"/>
-    </row>
-    <row r="67" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="J66" s="9"/>
+      <c r="K66" s="4"/>
+    </row>
+    <row r="67" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="6">
         <v>49</v>
@@ -4805,16 +4864,17 @@
       <c r="F67" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G67" s="3" t="s">
-        <v>10</v>
+      <c r="G67" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H67" s="6"/>
-      <c r="I67" s="11">
+      <c r="I67" s="10">
         <v>35830</v>
       </c>
-      <c r="J67" s="10"/>
-    </row>
-    <row r="68" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J67" s="9"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="6">
         <v>50</v>
@@ -4837,12 +4897,13 @@
       <c r="H68" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="10">
         <v>42662</v>
       </c>
-      <c r="J68" s="10"/>
-    </row>
-    <row r="69" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="J68" s="9"/>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="6">
         <v>51</v>
@@ -4859,16 +4920,17 @@
       <c r="F69" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G69" s="23" t="s">
-        <v>579</v>
+      <c r="G69" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H69" s="6"/>
-      <c r="I69" s="11">
+      <c r="I69" s="10">
         <v>37874</v>
       </c>
-      <c r="J69" s="10"/>
-    </row>
-    <row r="70" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="J69" s="9"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="6">
         <v>52</v>
@@ -4880,7 +4942,7 @@
         <v>172</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>110</v>
@@ -4891,12 +4953,13 @@
       <c r="H70" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="10">
         <v>35842</v>
       </c>
-      <c r="J70" s="10"/>
-    </row>
-    <row r="71" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="J70" s="9"/>
+      <c r="K70" s="4"/>
+    </row>
+    <row r="71" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="6">
         <v>53</v>
@@ -4908,7 +4971,7 @@
         <v>174</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>110</v>
@@ -4919,12 +4982,13 @@
       <c r="H71" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I71" s="10">
         <v>38567</v>
       </c>
-      <c r="J71" s="10"/>
-    </row>
-    <row r="72" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="J71" s="9"/>
+      <c r="K71" s="4"/>
+    </row>
+    <row r="72" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="6">
         <v>54</v>
@@ -4947,12 +5011,13 @@
       <c r="H72" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I72" s="11">
+      <c r="I72" s="10">
         <v>44188</v>
       </c>
-      <c r="J72" s="10"/>
-    </row>
-    <row r="73" spans="1:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="J72" s="9"/>
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="6">
         <v>55</v>
@@ -4975,14 +5040,15 @@
       <c r="H73" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="10">
         <v>45044</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="303.60000000000002" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" ht="303.60000000000002" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="6">
         <v>56</v>
@@ -4994,21 +5060,22 @@
         <v>182</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H74" s="6"/>
-      <c r="I74" s="11">
+      <c r="I74" s="10">
         <v>45034</v>
       </c>
-      <c r="J74" s="10"/>
-    </row>
-    <row r="75" spans="1:10" ht="196.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J74" s="9"/>
+      <c r="K74" s="4"/>
+    </row>
+    <row r="75" spans="1:11" ht="196.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4"/>
       <c r="B75" s="6">
         <v>57</v>
@@ -5020,23 +5087,24 @@
         <v>184</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G75" s="23" t="s">
-        <v>579</v>
+      <c r="G75" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I75" s="11">
+      <c r="I75" s="10">
         <v>45020</v>
       </c>
-      <c r="J75" s="10"/>
-    </row>
-    <row r="76" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="J75" s="9"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="6">
         <v>58</v>
@@ -5057,12 +5125,13 @@
         <v>10</v>
       </c>
       <c r="H76" s="6"/>
-      <c r="I76" s="11">
+      <c r="I76" s="10">
         <v>45062</v>
       </c>
-      <c r="J76" s="10"/>
-    </row>
-    <row r="77" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="J76" s="9"/>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A77" s="4"/>
       <c r="B77" s="6">
         <v>59</v>
@@ -5074,21 +5143,22 @@
         <v>189</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G77" s="23" t="s">
-        <v>579</v>
+      <c r="G77" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H77" s="6"/>
-      <c r="I77" s="11">
+      <c r="I77" s="10">
         <v>44966</v>
       </c>
-      <c r="J77" s="10"/>
-    </row>
-    <row r="78" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J77" s="9"/>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A78" s="4"/>
       <c r="B78" s="6">
         <v>60</v>
@@ -5111,12 +5181,15 @@
       <c r="H78" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I78" s="11">
+      <c r="I78" s="10">
         <v>44188</v>
       </c>
-      <c r="J78" s="10"/>
-    </row>
-    <row r="79" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J78" s="9"/>
+      <c r="K78" s="21">
+        <v>44210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="6">
         <v>61</v>
@@ -5139,12 +5212,15 @@
       <c r="H79" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="10">
         <v>39218</v>
       </c>
-      <c r="J79" s="10"/>
-    </row>
-    <row r="80" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J79" s="9"/>
+      <c r="K79" s="21">
+        <v>39279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A80" s="4"/>
       <c r="B80" s="6">
         <v>62</v>
@@ -5159,18 +5235,21 @@
       <c r="F80" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G80" s="3" t="s">
-        <v>10</v>
+      <c r="G80" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="10">
         <v>42174</v>
       </c>
-      <c r="J80" s="10"/>
-    </row>
-    <row r="81" spans="1:10" ht="207" x14ac:dyDescent="0.25">
+      <c r="J80" s="9"/>
+      <c r="K80" s="21">
+        <v>42202</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="207" x14ac:dyDescent="0.25">
       <c r="A81" s="4"/>
       <c r="B81" s="6">
         <v>63</v>
@@ -5193,12 +5272,15 @@
       <c r="H81" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="10">
         <v>41975</v>
       </c>
-      <c r="J81" s="10"/>
-    </row>
-    <row r="82" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J81" s="9"/>
+      <c r="K81" s="21">
+        <v>42032</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A82" s="4"/>
       <c r="B82" s="6">
         <v>64</v>
@@ -5221,12 +5303,15 @@
       <c r="H82" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="10">
         <v>42384</v>
       </c>
-      <c r="J82" s="10"/>
-    </row>
-    <row r="83" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J82" s="9"/>
+      <c r="K82" s="21">
+        <v>42405</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="6">
         <v>65</v>
@@ -5249,14 +5334,15 @@
       <c r="H83" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="10">
         <v>44211</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="234.6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" spans="1:11" ht="234.6" x14ac:dyDescent="0.25">
       <c r="A84" s="4"/>
       <c r="B84" s="6">
         <v>66</v>
@@ -5279,14 +5365,17 @@
       <c r="H84" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="10">
         <v>44449</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K84" s="21">
+        <v>44467</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B85" s="6">
         <v>67</v>
       </c>
@@ -5297,25 +5386,26 @@
         <v>211</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G85" s="23" t="s">
-        <v>579</v>
+      <c r="G85" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="10">
         <v>44475</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="207" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K85" s="4"/>
+    </row>
+    <row r="86" spans="1:11" ht="207" x14ac:dyDescent="0.25">
       <c r="B86" s="6">
         <v>68</v>
       </c>
@@ -5337,12 +5427,15 @@
       <c r="H86" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="10">
         <v>44736</v>
       </c>
-      <c r="J86" s="10"/>
-    </row>
-    <row r="87" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J86" s="9"/>
+      <c r="K86" s="21">
+        <v>44753</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B87" s="6">
         <v>69</v>
       </c>
@@ -5362,23 +5455,24 @@
         <v>10</v>
       </c>
       <c r="H87" s="6"/>
-      <c r="I87" s="11">
+      <c r="I87" s="10">
         <v>45075</v>
       </c>
-      <c r="J87" s="10"/>
-    </row>
-    <row r="88" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="J87" s="9"/>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B88" s="6">
         <v>70</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D88" s="22" t="s">
-        <v>581</v>
+      <c r="D88" s="25" t="s">
+        <v>573</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>197</v>
@@ -5389,12 +5483,13 @@
       <c r="H88" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="10">
         <v>45110</v>
       </c>
-      <c r="J88" s="10"/>
-    </row>
-    <row r="89" spans="1:10" ht="289.8" x14ac:dyDescent="0.25">
+      <c r="J88" s="9"/>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="1:11" ht="289.8" x14ac:dyDescent="0.25">
       <c r="B89" s="6">
         <v>71</v>
       </c>
@@ -5405,21 +5500,22 @@
         <v>220</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G89" s="23" t="s">
-        <v>579</v>
+      <c r="G89" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H89" s="6"/>
-      <c r="I89" s="11">
+      <c r="I89" s="10">
         <v>45121</v>
       </c>
-      <c r="J89" s="10"/>
-    </row>
-    <row r="90" spans="1:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="J89" s="9"/>
+      <c r="K89" s="4"/>
+    </row>
+    <row r="90" spans="1:11" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B90" s="6">
         <v>72</v>
       </c>
@@ -5439,12 +5535,15 @@
         <v>10</v>
       </c>
       <c r="H90" s="6"/>
-      <c r="I90" s="11">
+      <c r="I90" s="10">
         <v>39167</v>
       </c>
-      <c r="J90" s="10"/>
-    </row>
-    <row r="91" spans="1:10" ht="220.8" x14ac:dyDescent="0.25">
+      <c r="J90" s="9"/>
+      <c r="K90" s="21">
+        <v>39182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="220.8" x14ac:dyDescent="0.25">
       <c r="B91" s="6">
         <v>73</v>
       </c>
@@ -5464,12 +5563,15 @@
         <v>10</v>
       </c>
       <c r="H91" s="6"/>
-      <c r="I91" s="11">
+      <c r="I91" s="10">
         <v>39196</v>
       </c>
-      <c r="J91" s="10"/>
-    </row>
-    <row r="92" spans="1:10" ht="289.8" x14ac:dyDescent="0.25">
+      <c r="J91" s="9"/>
+      <c r="K91" s="21">
+        <v>39216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="289.8" x14ac:dyDescent="0.25">
       <c r="B92" s="6">
         <v>74</v>
       </c>
@@ -5491,12 +5593,15 @@
       <c r="H92" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I92" s="11">
+      <c r="I92" s="10">
         <v>39609</v>
       </c>
-      <c r="J92" s="10"/>
-    </row>
-    <row r="93" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J92" s="9"/>
+      <c r="K92" s="21">
+        <v>39636</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B93" s="6">
         <v>75</v>
       </c>
@@ -5507,7 +5612,7 @@
         <v>230</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>231</v>
@@ -5518,12 +5623,13 @@
       <c r="H93" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I93" s="11">
+      <c r="I93" s="10">
         <v>35065</v>
       </c>
-      <c r="J93" s="10"/>
-    </row>
-    <row r="94" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J93" s="9"/>
+      <c r="K93" s="4"/>
+    </row>
+    <row r="94" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B94" s="6">
         <v>76</v>
       </c>
@@ -5534,7 +5640,7 @@
         <v>233</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>231</v>
@@ -5545,12 +5651,13 @@
       <c r="H94" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I94" s="11">
+      <c r="I94" s="10">
         <v>35065</v>
       </c>
-      <c r="J94" s="10"/>
-    </row>
-    <row r="95" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J94" s="9"/>
+      <c r="K94" s="4"/>
+    </row>
+    <row r="95" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B95" s="6">
         <v>77</v>
       </c>
@@ -5561,7 +5668,7 @@
         <v>235</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>231</v>
@@ -5572,12 +5679,13 @@
       <c r="H95" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I95" s="11">
+      <c r="I95" s="10">
         <v>35431</v>
       </c>
-      <c r="J95" s="10"/>
-    </row>
-    <row r="96" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J95" s="9"/>
+      <c r="K95" s="4"/>
+    </row>
+    <row r="96" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B96" s="6">
         <v>78</v>
       </c>
@@ -5597,14 +5705,15 @@
       <c r="H96" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I96" s="11">
+      <c r="I96" s="10">
         <v>36161</v>
       </c>
-      <c r="J96" s="10"/>
-    </row>
-    <row r="97" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J96" s="9"/>
+      <c r="K96" s="4"/>
+    </row>
+    <row r="97" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B97" s="6">
         <v>79</v>
@@ -5625,12 +5734,13 @@
       <c r="H97" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="I97" s="11">
+      <c r="I97" s="10">
         <v>36161</v>
       </c>
-      <c r="J97" s="10"/>
-    </row>
-    <row r="98" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J97" s="9"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B98" s="6">
         <v>80</v>
       </c>
@@ -5650,12 +5760,13 @@
       <c r="H98" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I98" s="11">
+      <c r="I98" s="10">
         <v>36526</v>
       </c>
-      <c r="J98" s="10"/>
-    </row>
-    <row r="99" spans="1:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="J98" s="9"/>
+      <c r="K98" s="4"/>
+    </row>
+    <row r="99" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B99" s="6">
         <v>81</v>
       </c>
@@ -5675,12 +5786,13 @@
       <c r="H99" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I99" s="11">
+      <c r="I99" s="10">
         <v>39448</v>
       </c>
-      <c r="J99" s="10"/>
-    </row>
-    <row r="100" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J99" s="9"/>
+      <c r="K99" s="4"/>
+    </row>
+    <row r="100" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B100" s="6">
         <v>82</v>
       </c>
@@ -5700,12 +5812,13 @@
       <c r="H100" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="I100" s="11">
+      <c r="I100" s="10">
         <v>36526</v>
       </c>
-      <c r="J100" s="10"/>
-    </row>
-    <row r="101" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J100" s="9"/>
+      <c r="K100" s="4"/>
+    </row>
+    <row r="101" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B101" s="6">
         <v>83</v>
       </c>
@@ -5725,12 +5838,13 @@
       <c r="H101" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I101" s="11">
+      <c r="I101" s="10">
         <v>40909</v>
       </c>
-      <c r="J101" s="10"/>
-    </row>
-    <row r="102" spans="1:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="J101" s="9"/>
+      <c r="K101" s="4"/>
+    </row>
+    <row r="102" spans="1:11" ht="165.6" x14ac:dyDescent="0.25">
       <c r="B102" s="6">
         <v>84</v>
       </c>
@@ -5751,12 +5865,13 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I102" s="11">
+      <c r="I102" s="10">
         <v>37622</v>
       </c>
-      <c r="J102" s="10"/>
-    </row>
-    <row r="103" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J102" s="9"/>
+      <c r="K102" s="4"/>
+    </row>
+    <row r="103" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B103" s="6">
         <v>85</v>
       </c>
@@ -5765,7 +5880,7 @@
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>238</v>
@@ -5776,12 +5891,13 @@
       <c r="H103" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I103" s="11">
+      <c r="I103" s="10">
         <v>37987</v>
       </c>
-      <c r="J103" s="10"/>
-    </row>
-    <row r="104" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J103" s="9"/>
+      <c r="K103" s="4"/>
+    </row>
+    <row r="104" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B104" s="6">
         <v>86</v>
       </c>
@@ -5801,12 +5917,13 @@
       <c r="H104" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I104" s="11">
+      <c r="I104" s="10">
         <v>41275</v>
       </c>
-      <c r="J104" s="10"/>
-    </row>
-    <row r="105" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J104" s="9"/>
+      <c r="K104" s="4"/>
+    </row>
+    <row r="105" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B105" s="6">
         <v>87</v>
       </c>
@@ -5815,7 +5932,7 @@
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>238</v>
@@ -5826,12 +5943,13 @@
       <c r="H105" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I105" s="11">
+      <c r="I105" s="10">
         <v>42005</v>
       </c>
-      <c r="J105" s="10"/>
-    </row>
-    <row r="106" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J105" s="9"/>
+      <c r="K105" s="4"/>
+    </row>
+    <row r="106" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B106" s="6">
         <v>88</v>
       </c>
@@ -5840,7 +5958,7 @@
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>238</v>
@@ -5851,12 +5969,13 @@
       <c r="H106" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I106" s="11">
+      <c r="I106" s="10">
         <v>42005</v>
       </c>
-      <c r="J106" s="10"/>
-    </row>
-    <row r="107" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J106" s="9"/>
+      <c r="K106" s="4"/>
+    </row>
+    <row r="107" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B107" s="6">
         <v>89</v>
       </c>
@@ -5865,7 +5984,7 @@
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>238</v>
@@ -5876,12 +5995,13 @@
       <c r="H107" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I107" s="11">
+      <c r="I107" s="10">
         <v>42005</v>
       </c>
-      <c r="J107" s="10"/>
-    </row>
-    <row r="108" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J107" s="9"/>
+      <c r="K107" s="4"/>
+    </row>
+    <row r="108" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B108" s="6">
         <v>90</v>
       </c>
@@ -5890,7 +6010,7 @@
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>238</v>
@@ -5901,12 +6021,13 @@
       <c r="H108" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I108" s="11">
+      <c r="I108" s="10">
         <v>42005</v>
       </c>
-      <c r="J108" s="10"/>
-    </row>
-    <row r="109" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J108" s="9"/>
+      <c r="K108" s="4"/>
+    </row>
+    <row r="109" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B109" s="6">
         <v>91</v>
       </c>
@@ -5926,12 +6047,13 @@
       <c r="H109" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I109" s="11">
+      <c r="I109" s="10">
         <v>36892</v>
       </c>
-      <c r="J109" s="10"/>
-    </row>
-    <row r="110" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="J109" s="9"/>
+      <c r="K109" s="4"/>
+    </row>
+    <row r="110" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="B110" s="6">
         <v>92</v>
       </c>
@@ -5952,12 +6074,13 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I110" s="11">
+      <c r="I110" s="10">
         <v>36892</v>
       </c>
-      <c r="J110" s="10"/>
-    </row>
-    <row r="111" spans="1:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="J110" s="9"/>
+      <c r="K110" s="4"/>
+    </row>
+    <row r="111" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="B111" s="6">
         <v>93</v>
       </c>
@@ -5978,12 +6101,13 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I111" s="11">
+      <c r="I111" s="10">
         <v>36892</v>
       </c>
-      <c r="J111" s="10"/>
-    </row>
-    <row r="112" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J111" s="9"/>
+      <c r="K111" s="4"/>
+    </row>
+    <row r="112" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B112" s="6">
         <v>94</v>
       </c>
@@ -6003,12 +6127,13 @@
       <c r="H112" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I112" s="11">
+      <c r="I112" s="10">
         <v>36892</v>
       </c>
-      <c r="J112" s="10"/>
-    </row>
-    <row r="113" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="J112" s="9"/>
+      <c r="K112" s="4"/>
+    </row>
+    <row r="113" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B113" s="6">
         <v>95</v>
       </c>
@@ -6017,7 +6142,7 @@
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>238</v>
@@ -6028,12 +6153,13 @@
       <c r="H113" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I113" s="11">
+      <c r="I113" s="10">
         <v>36892</v>
       </c>
-      <c r="J113" s="10"/>
-    </row>
-    <row r="114" spans="1:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J113" s="9"/>
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B114" s="6">
         <v>96</v>
       </c>
@@ -6053,12 +6179,13 @@
       <c r="H114" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I114" s="11">
+      <c r="I114" s="10">
         <v>36892</v>
       </c>
-      <c r="J114" s="10"/>
-    </row>
-    <row r="115" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J114" s="9"/>
+      <c r="K114" s="4"/>
+    </row>
+    <row r="115" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B115" s="6">
         <v>97</v>
       </c>
@@ -6067,7 +6194,7 @@
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>238</v>
@@ -6078,12 +6205,13 @@
       <c r="H115" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I115" s="11">
+      <c r="I115" s="10">
         <v>42005</v>
       </c>
-      <c r="J115" s="10"/>
-    </row>
-    <row r="116" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J115" s="9"/>
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B116" s="6">
         <v>98</v>
       </c>
@@ -6092,7 +6220,7 @@
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>238</v>
@@ -6103,12 +6231,13 @@
       <c r="H116" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I116" s="11">
+      <c r="I116" s="10">
         <v>42005</v>
       </c>
-      <c r="J116" s="10"/>
-    </row>
-    <row r="117" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J116" s="9"/>
+      <c r="K116" s="4"/>
+    </row>
+    <row r="117" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B117" s="6">
         <v>99</v>
       </c>
@@ -6117,7 +6246,7 @@
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>238</v>
@@ -6128,12 +6257,13 @@
       <c r="H117" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I117" s="11">
+      <c r="I117" s="10">
         <v>42005</v>
       </c>
-      <c r="J117" s="10"/>
-    </row>
-    <row r="118" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J117" s="9"/>
+      <c r="K117" s="4"/>
+    </row>
+    <row r="118" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B118" s="6">
         <v>100</v>
       </c>
@@ -6142,7 +6272,7 @@
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>238</v>
@@ -6153,23 +6283,24 @@
       <c r="H118" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I118" s="11">
+      <c r="I118" s="10">
         <v>42005</v>
       </c>
-      <c r="J118" s="10"/>
-    </row>
-    <row r="119" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J118" s="9"/>
+      <c r="K118" s="4"/>
+    </row>
+    <row r="119" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B119" s="6">
         <v>101</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E119" s="6"/>
       <c r="F119" s="6" t="s">
@@ -6182,20 +6313,21 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I119" s="11">
+      <c r="I119" s="10">
         <v>45292</v>
       </c>
-      <c r="J119" s="10"/>
-    </row>
-    <row r="120" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J119" s="9"/>
+      <c r="K119" s="4"/>
+    </row>
+    <row r="120" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B120" s="6">
         <v>102</v>
       </c>
       <c r="C120" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>407</v>
       </c>
       <c r="E120" s="6"/>
       <c r="F120" s="6" t="s">
@@ -6208,20 +6340,21 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I120" s="11">
+      <c r="I120" s="10">
         <v>45292</v>
       </c>
-      <c r="J120" s="10"/>
-    </row>
-    <row r="121" spans="1:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J120" s="9"/>
+      <c r="K120" s="4"/>
+    </row>
+    <row r="121" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B121" s="6">
         <v>103</v>
       </c>
       <c r="C121" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>408</v>
       </c>
       <c r="E121" s="6"/>
       <c r="F121" s="6" t="s">
@@ -6234,12 +6367,13 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I121" s="11">
+      <c r="I121" s="10">
         <v>45292</v>
       </c>
-      <c r="J121" s="10"/>
-    </row>
-    <row r="122" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J121" s="9"/>
+      <c r="K121" s="4"/>
+    </row>
+    <row r="122" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B122" s="6">
         <v>104</v>
       </c>
@@ -6248,7 +6382,7 @@
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>238</v>
@@ -6259,12 +6393,13 @@
       <c r="H122" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I122" s="11">
+      <c r="I122" s="10">
         <v>42005</v>
       </c>
-      <c r="J122" s="10"/>
-    </row>
-    <row r="123" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J122" s="9"/>
+      <c r="K122" s="4"/>
+    </row>
+    <row r="123" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B123" s="6">
         <v>105</v>
       </c>
@@ -6273,7 +6408,7 @@
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>238</v>
@@ -6284,12 +6419,13 @@
       <c r="H123" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I123" s="11">
+      <c r="I123" s="10">
         <v>42005</v>
       </c>
-      <c r="J123" s="10"/>
-    </row>
-    <row r="124" spans="1:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J123" s="9"/>
+      <c r="K123" s="4"/>
+    </row>
+    <row r="124" spans="1:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B124" s="6">
         <v>106</v>
       </c>
@@ -6298,7 +6434,7 @@
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>238</v>
@@ -6309,12 +6445,13 @@
       <c r="H124" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I124" s="11">
+      <c r="I124" s="10">
         <v>42005</v>
       </c>
-      <c r="J124" s="10"/>
-    </row>
-    <row r="125" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J124" s="9"/>
+      <c r="K124" s="4"/>
+    </row>
+    <row r="125" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B125" s="6">
         <v>107</v>
       </c>
@@ -6334,12 +6471,13 @@
       <c r="H125" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I125" s="11">
+      <c r="I125" s="10">
         <v>36161</v>
       </c>
-      <c r="J125" s="10"/>
-    </row>
-    <row r="126" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J125" s="9"/>
+      <c r="K125" s="4"/>
+    </row>
+    <row r="126" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B126" s="6">
         <v>108</v>
       </c>
@@ -6359,12 +6497,13 @@
       <c r="H126" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I126" s="11">
+      <c r="I126" s="10">
         <v>36161</v>
       </c>
-      <c r="J126" s="10"/>
-    </row>
-    <row r="127" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="J126" s="9"/>
+      <c r="K126" s="4"/>
+    </row>
+    <row r="127" spans="1:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B127" s="6">
         <v>109</v>
       </c>
@@ -6384,12 +6523,13 @@
       <c r="H127" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I127" s="11">
+      <c r="I127" s="10">
         <v>36161</v>
       </c>
-      <c r="J127" s="10"/>
-    </row>
-    <row r="128" spans="1:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J127" s="9"/>
+      <c r="K127" s="4"/>
+    </row>
+    <row r="128" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B128" s="6">
         <v>110</v>
       </c>
@@ -6409,12 +6549,13 @@
       <c r="H128" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I128" s="11">
+      <c r="I128" s="10">
         <v>37257</v>
       </c>
-      <c r="J128" s="10"/>
-    </row>
-    <row r="129" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J128" s="9"/>
+      <c r="K128" s="4"/>
+    </row>
+    <row r="129" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B129" s="6">
         <v>111</v>
       </c>
@@ -6434,12 +6575,13 @@
       <c r="H129" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I129" s="11">
+      <c r="I129" s="10">
         <v>37622</v>
       </c>
-      <c r="J129" s="10"/>
-    </row>
-    <row r="130" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J129" s="9"/>
+      <c r="K129" s="4"/>
+    </row>
+    <row r="130" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B130" s="6">
         <v>112</v>
       </c>
@@ -6448,7 +6590,7 @@
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>238</v>
@@ -6459,12 +6601,13 @@
       <c r="H130" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I130" s="11">
+      <c r="I130" s="10">
         <v>42005</v>
       </c>
-      <c r="J130" s="10"/>
-    </row>
-    <row r="131" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J130" s="9"/>
+      <c r="K130" s="4"/>
+    </row>
+    <row r="131" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B131" s="6">
         <v>113</v>
       </c>
@@ -6484,12 +6627,13 @@
       <c r="H131" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I131" s="11">
+      <c r="I131" s="10">
         <v>40544</v>
       </c>
-      <c r="J131" s="10"/>
-    </row>
-    <row r="132" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="J131" s="9"/>
+      <c r="K131" s="4"/>
+    </row>
+    <row r="132" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B132" s="6">
         <v>114</v>
       </c>
@@ -6510,12 +6654,13 @@
         <f>"#ТЗІ"</f>
         <v>#ТЗІ</v>
       </c>
-      <c r="I132" s="11">
+      <c r="I132" s="10">
         <v>44197</v>
       </c>
-      <c r="J132" s="10"/>
-    </row>
-    <row r="133" spans="2:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="J132" s="9"/>
+      <c r="K132" s="4"/>
+    </row>
+    <row r="133" spans="2:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B133" s="6">
         <v>115</v>
       </c>
@@ -6535,12 +6680,13 @@
       <c r="H133" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I133" s="11">
+      <c r="I133" s="10">
         <v>36161</v>
       </c>
-      <c r="J133" s="10"/>
-    </row>
-    <row r="134" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J133" s="9"/>
+      <c r="K133" s="4"/>
+    </row>
+    <row r="134" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B134" s="6">
         <v>116</v>
       </c>
@@ -6560,12 +6706,13 @@
       <c r="H134" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I134" s="11">
+      <c r="I134" s="10">
         <v>39814</v>
       </c>
-      <c r="J134" s="10"/>
-    </row>
-    <row r="135" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J134" s="9"/>
+      <c r="K134" s="4"/>
+    </row>
+    <row r="135" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B135" s="6">
         <v>117</v>
       </c>
@@ -6585,12 +6732,13 @@
       <c r="H135" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I135" s="11">
+      <c r="I135" s="10">
         <v>39814</v>
       </c>
-      <c r="J135" s="10"/>
-    </row>
-    <row r="136" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J135" s="9"/>
+      <c r="K135" s="4"/>
+    </row>
+    <row r="136" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B136" s="6">
         <v>118</v>
       </c>
@@ -6610,12 +6758,13 @@
       <c r="H136" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I136" s="11">
+      <c r="I136" s="10">
         <v>40909</v>
       </c>
-      <c r="J136" s="10"/>
-    </row>
-    <row r="137" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="J136" s="9"/>
+      <c r="K136" s="4"/>
+    </row>
+    <row r="137" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B137" s="6">
         <v>119</v>
       </c>
@@ -6624,7 +6773,7 @@
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>238</v>
@@ -6635,12 +6784,13 @@
       <c r="H137" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I137" s="11">
+      <c r="I137" s="10">
         <v>42005</v>
       </c>
-      <c r="J137" s="10"/>
-    </row>
-    <row r="138" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="J137" s="9"/>
+      <c r="K137" s="4"/>
+    </row>
+    <row r="138" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B138" s="6">
         <v>120</v>
       </c>
@@ -6648,7 +6798,9 @@
         <v>302</v>
       </c>
       <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
+      <c r="E138" s="6" t="s">
+        <v>408</v>
+      </c>
       <c r="F138" s="6" t="s">
         <v>238</v>
       </c>
@@ -6658,45 +6810,48 @@
       <c r="H138" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I138" s="11">
-        <v>36526</v>
-      </c>
-      <c r="J138" s="10"/>
-    </row>
-    <row r="139" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="I138" s="10">
+        <v>42370</v>
+      </c>
+      <c r="J138" s="9"/>
+      <c r="K138" s="4"/>
+    </row>
+    <row r="139" spans="2:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B139" s="6">
         <v>121</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6" t="s">
-        <v>410</v>
-      </c>
+      <c r="D139" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E139" s="6"/>
       <c r="F139" s="6" t="s">
         <v>238</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H139" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I139" s="11">
-        <v>42370</v>
-      </c>
-      <c r="J139" s="10"/>
-    </row>
-    <row r="140" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="H139" s="6" t="str">
+        <f t="shared" ref="H139:H144" si="0">"#ТЗІ"</f>
+        <v>#ТЗІ</v>
+      </c>
+      <c r="I139" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J139" s="9"/>
+      <c r="K139" s="4"/>
+    </row>
+    <row r="140" spans="2:11" ht="165.6" x14ac:dyDescent="0.25">
       <c r="B140" s="6">
         <v>122</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E140" s="6"/>
       <c r="F140" s="6" t="s">
@@ -6706,23 +6861,24 @@
         <v>10</v>
       </c>
       <c r="H140" s="6" t="str">
-        <f t="shared" ref="H140:H145" si="0">"#ТЗІ"</f>
+        <f t="shared" si="0"/>
         <v>#ТЗІ</v>
       </c>
-      <c r="I140" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J140" s="10"/>
-    </row>
-    <row r="141" spans="2:10" ht="165.6" x14ac:dyDescent="0.25">
+      <c r="I140" s="10">
+        <v>36526</v>
+      </c>
+      <c r="J140" s="9"/>
+      <c r="K140" s="4"/>
+    </row>
+    <row r="141" spans="2:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B141" s="6">
         <v>123</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E141" s="6"/>
       <c r="F141" s="6" t="s">
@@ -6735,20 +6891,21 @@
         <f t="shared" si="0"/>
         <v>#ТЗІ</v>
       </c>
-      <c r="I141" s="11">
-        <v>36526</v>
-      </c>
-      <c r="J141" s="10"/>
-    </row>
-    <row r="142" spans="2:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="I141" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J141" s="9"/>
+      <c r="K141" s="4"/>
+    </row>
+    <row r="142" spans="2:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B142" s="6">
         <v>124</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="6" t="s">
@@ -6761,20 +6918,21 @@
         <f t="shared" si="0"/>
         <v>#ТЗІ</v>
       </c>
-      <c r="I142" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J142" s="10"/>
-    </row>
-    <row r="143" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I142" s="10">
+        <v>45292</v>
+      </c>
+      <c r="J142" s="9"/>
+      <c r="K142" s="4"/>
+    </row>
+    <row r="143" spans="2:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B143" s="6">
         <v>125</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="E143" s="6"/>
       <c r="F143" s="6" t="s">
@@ -6787,20 +6945,21 @@
         <f t="shared" si="0"/>
         <v>#ТЗІ</v>
       </c>
-      <c r="I143" s="11">
+      <c r="I143" s="10">
         <v>45292</v>
       </c>
-      <c r="J143" s="10"/>
-    </row>
-    <row r="144" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J143" s="9"/>
+      <c r="K143" s="4"/>
+    </row>
+    <row r="144" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B144" s="6">
         <v>126</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6" t="s">
@@ -6813,20 +6972,21 @@
         <f t="shared" si="0"/>
         <v>#ТЗІ</v>
       </c>
-      <c r="I144" s="11">
+      <c r="I144" s="10">
         <v>45292</v>
       </c>
-      <c r="J144" s="10"/>
-    </row>
-    <row r="145" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="J144" s="9"/>
+      <c r="K144" s="4"/>
+    </row>
+    <row r="145" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B145" s="6">
         <v>127</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E145" s="6"/>
       <c r="F145" s="6" t="s">
@@ -6835,24 +6995,24 @@
       <c r="G145" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H145" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>#ТЗІ</v>
-      </c>
-      <c r="I145" s="11">
-        <v>45292</v>
-      </c>
-      <c r="J145" s="10"/>
-    </row>
-    <row r="146" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="H145" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I145" s="10">
+        <v>36161</v>
+      </c>
+      <c r="J145" s="9"/>
+      <c r="K145" s="4"/>
+    </row>
+    <row r="146" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B146" s="6">
         <v>128</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E146" s="6"/>
       <c r="F146" s="6" t="s">
@@ -6864,20 +7024,21 @@
       <c r="H146" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I146" s="11">
-        <v>36161</v>
-      </c>
-      <c r="J146" s="10"/>
-    </row>
-    <row r="147" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="I146" s="10">
+        <v>44927</v>
+      </c>
+      <c r="J146" s="9"/>
+      <c r="K146" s="4"/>
+    </row>
+    <row r="147" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B147" s="6">
         <v>129</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="E147" s="6"/>
       <c r="F147" s="6" t="s">
@@ -6886,23 +7047,25 @@
       <c r="G147" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H147" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="I147" s="11">
-        <v>44927</v>
-      </c>
-      <c r="J147" s="10"/>
-    </row>
-    <row r="148" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="H147" s="6" t="str">
+        <f>"#ТЗІ"</f>
+        <v>#ТЗІ</v>
+      </c>
+      <c r="I147" s="10">
+        <v>36892</v>
+      </c>
+      <c r="J147" s="9"/>
+      <c r="K147" s="4"/>
+    </row>
+    <row r="148" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B148" s="6">
         <v>130</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6" t="s">
@@ -6911,24 +7074,24 @@
       <c r="G148" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H148" s="6" t="str">
-        <f>"#ТЗІ"</f>
-        <v>#ТЗІ</v>
-      </c>
-      <c r="I148" s="11">
-        <v>36892</v>
-      </c>
-      <c r="J148" s="10"/>
-    </row>
-    <row r="149" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="H148" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I148" s="10">
+        <v>36526</v>
+      </c>
+      <c r="J148" s="9"/>
+      <c r="K148" s="4"/>
+    </row>
+    <row r="149" spans="2:11" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B149" s="6">
         <v>131</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E149" s="6"/>
       <c r="F149" s="6" t="s">
@@ -6940,1046 +7103,1090 @@
       <c r="H149" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="I149" s="11">
-        <v>36526</v>
-      </c>
-      <c r="J149" s="10"/>
-    </row>
-    <row r="150" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="I149" s="10">
+        <v>34700</v>
+      </c>
+      <c r="J149" s="9"/>
+      <c r="K149" s="4"/>
+    </row>
+    <row r="150" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B150" s="6">
         <v>132</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D150" s="6" t="s">
+      <c r="C150" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6" t="s">
+      <c r="D150" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7" t="s">
         <v>238</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H150" s="6" t="s">
+      <c r="H150" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="I150" s="11">
+      <c r="I150" s="10">
         <v>34700</v>
       </c>
-      <c r="J150" s="10"/>
-    </row>
-    <row r="151" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="J150" s="9"/>
+      <c r="K150" s="4"/>
+    </row>
+    <row r="151" spans="2:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B151" s="6">
         <v>133</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E151" s="7"/>
-      <c r="F151" s="7" t="s">
-        <v>238</v>
+      <c r="F151" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I151" s="11">
-        <v>34700</v>
-      </c>
-      <c r="J151" s="10"/>
-    </row>
-    <row r="152" spans="2:10" ht="55.2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="I151" s="10">
+        <v>45467</v>
+      </c>
+      <c r="J151" s="9"/>
+      <c r="K151" s="4"/>
+    </row>
+    <row r="152" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B152" s="6">
         <v>134</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="E152" s="7"/>
+        <v>607</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>588</v>
+      </c>
       <c r="F152" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>10</v>
+      <c r="G152" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H152" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I152" s="11">
-        <v>45467</v>
-      </c>
-      <c r="J152" s="10"/>
-    </row>
-    <row r="153" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I152" s="10">
+        <v>45412</v>
+      </c>
+      <c r="J152" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="K152" s="21">
+        <v>45454</v>
+      </c>
+    </row>
+    <row r="153" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B153" s="6">
         <v>135</v>
       </c>
-      <c r="C153" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>596</v>
-      </c>
+      <c r="C153" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="E153" s="6"/>
       <c r="F153" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G153" s="23" t="s">
-        <v>579</v>
-      </c>
-      <c r="H153" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I153" s="11">
-        <v>45412</v>
-      </c>
-      <c r="J153" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="I153" s="10">
+        <v>43466</v>
+      </c>
+      <c r="J153" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K153" s="4"/>
+    </row>
+    <row r="154" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B154" s="6">
         <v>136</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>385</v>
+      <c r="C154" s="20" t="s">
+        <v>338</v>
       </c>
       <c r="E154" s="6"/>
       <c r="F154" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G154" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I154" s="11">
+        <v>386</v>
+      </c>
+      <c r="I154" s="10">
         <v>43466</v>
       </c>
-      <c r="J154" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J154" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K154" s="4"/>
+    </row>
+    <row r="155" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B155" s="6">
         <v>137</v>
       </c>
-      <c r="C155" s="9" t="s">
-        <v>340</v>
+      <c r="C155" s="19" t="s">
+        <v>376</v>
       </c>
       <c r="E155" s="6"/>
       <c r="F155" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I155" s="11">
-        <v>43466</v>
-      </c>
-      <c r="J155" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I155" s="10">
+        <v>42736</v>
+      </c>
+      <c r="J155" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K155" s="4"/>
+    </row>
+    <row r="156" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B156" s="6">
         <v>138</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>378</v>
+      <c r="C156" s="19" t="s">
+        <v>377</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I156" s="11">
+        <v>386</v>
+      </c>
+      <c r="I156" s="10">
         <v>42736</v>
       </c>
-      <c r="J156" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J156" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K156" s="4"/>
+    </row>
+    <row r="157" spans="2:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B157" s="6">
         <v>139</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>379</v>
+      <c r="C157" s="19" t="s">
+        <v>381</v>
       </c>
       <c r="E157" s="6"/>
       <c r="F157" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I157" s="11">
-        <v>42736</v>
-      </c>
-      <c r="J157" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I157" s="10">
+        <v>43466</v>
+      </c>
+      <c r="J157" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K157" s="4"/>
+    </row>
+    <row r="158" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B158" s="6">
         <v>140</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>383</v>
+      <c r="C158" s="19" t="s">
+        <v>340</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I158" s="11">
+        <v>386</v>
+      </c>
+      <c r="I158" s="10">
         <v>43466</v>
       </c>
-      <c r="J158" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J158" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K158" s="4"/>
+    </row>
+    <row r="159" spans="2:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B159" s="6">
         <v>141</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>342</v>
+      <c r="C159" s="19" t="s">
+        <v>337</v>
       </c>
       <c r="E159" s="6"/>
       <c r="F159" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I159" s="11">
-        <v>43466</v>
-      </c>
-      <c r="J159" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I159" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J159" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K159" s="4"/>
+    </row>
+    <row r="160" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B160" s="6">
         <v>142</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>339</v>
+      <c r="C160" s="19" t="s">
+        <v>382</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I160" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J160" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I160" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="J160" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K160" s="4"/>
+    </row>
+    <row r="161" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B161" s="6">
         <v>143</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>384</v>
+      <c r="C161" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>369</v>
       </c>
       <c r="E161" s="6"/>
       <c r="F161" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H161" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I161" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="J161" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I161" s="10">
+        <v>40179</v>
+      </c>
+      <c r="J161" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K161" s="4"/>
+    </row>
+    <row r="162" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B162" s="6">
         <v>144</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>371</v>
+      <c r="C162" s="19" t="s">
+        <v>341</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I162" s="11">
-        <v>40179</v>
-      </c>
-      <c r="J162" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I162" s="10">
+        <v>41640</v>
+      </c>
+      <c r="J162" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K162" s="4"/>
+    </row>
+    <row r="163" spans="2:11" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B163" s="6">
         <v>145</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>343</v>
+      <c r="C163" s="19" t="s">
+        <v>384</v>
       </c>
       <c r="E163" s="6"/>
       <c r="F163" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I163" s="11">
-        <v>41640</v>
-      </c>
-      <c r="J163" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I163" s="10">
+        <v>42005</v>
+      </c>
+      <c r="J163" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K163" s="4"/>
+    </row>
+    <row r="164" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B164" s="6">
         <v>146</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>386</v>
+      <c r="C164" s="19" t="s">
+        <v>339</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I164" s="11">
+        <v>386</v>
+      </c>
+      <c r="I164" s="10">
         <v>42005</v>
       </c>
-      <c r="J164" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J164" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K164" s="4"/>
+    </row>
+    <row r="165" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B165" s="6">
         <v>147</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>341</v>
+      <c r="C165" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="E165" s="6"/>
       <c r="F165" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H165" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I165" s="11">
-        <v>42005</v>
-      </c>
-      <c r="J165" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I165" s="10">
+        <v>36526</v>
+      </c>
+      <c r="J165" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K165" s="4"/>
+    </row>
+    <row r="166" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B166" s="6">
         <v>148</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>366</v>
+      <c r="C166" s="19" t="s">
+        <v>334</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E166" s="6"/>
       <c r="F166" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I166" s="11">
+        <v>386</v>
+      </c>
+      <c r="I166" s="10">
         <v>36526</v>
       </c>
-      <c r="J166" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J166" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K166" s="4"/>
+    </row>
+    <row r="167" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B167" s="6">
         <v>149</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>336</v>
+      <c r="C167" s="20" t="s">
+        <v>353</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E167" s="6"/>
       <c r="F167" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I167" s="11">
-        <v>36526</v>
-      </c>
-      <c r="J167" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I167" s="10">
+        <v>36892</v>
+      </c>
+      <c r="J167" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K167" s="4"/>
+    </row>
+    <row r="168" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B168" s="6">
         <v>150</v>
       </c>
-      <c r="C168" s="9" t="s">
-        <v>355</v>
+      <c r="C168" s="20" t="s">
+        <v>335</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I168" s="11">
+        <v>386</v>
+      </c>
+      <c r="I168" s="10">
         <v>36892</v>
       </c>
-      <c r="J168" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J168" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K168" s="4"/>
+    </row>
+    <row r="169" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B169" s="6">
         <v>151</v>
       </c>
-      <c r="C169" s="9" t="s">
-        <v>337</v>
+      <c r="C169" s="19" t="s">
+        <v>354</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="E169" s="6"/>
       <c r="F169" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H169" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I169" s="11">
-        <v>36892</v>
-      </c>
-      <c r="J169" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I169" s="10">
+        <v>37257</v>
+      </c>
+      <c r="J169" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K169" s="4"/>
+    </row>
+    <row r="170" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B170" s="6">
         <v>152</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>356</v>
+      <c r="C170" s="19" t="s">
+        <v>333</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="E170" s="6"/>
       <c r="F170" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I170" s="11">
+        <v>386</v>
+      </c>
+      <c r="I170" s="10">
         <v>37257</v>
       </c>
-      <c r="J170" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J170" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K170" s="4"/>
+    </row>
+    <row r="171" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B171" s="6">
         <v>153</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>335</v>
+      <c r="C171" s="19" t="s">
+        <v>355</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E171" s="6"/>
+        <v>361</v>
+      </c>
+      <c r="E171" s="7"/>
       <c r="F171" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H171" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I171" s="11">
-        <v>37257</v>
-      </c>
-      <c r="J171" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I171" s="10">
+        <v>37622</v>
+      </c>
+      <c r="J171" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K171" s="4"/>
+    </row>
+    <row r="172" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B172" s="6">
         <v>154</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>357</v>
+      <c r="C172" s="19" t="s">
+        <v>356</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E172" s="7"/>
+        <v>347</v>
+      </c>
+      <c r="E172" s="6"/>
       <c r="F172" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G172" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I172" s="11">
-        <v>37622</v>
-      </c>
-      <c r="J172" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I172" s="10">
+        <v>37987</v>
+      </c>
+      <c r="J172" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K172" s="4"/>
+    </row>
+    <row r="173" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B173" s="6">
         <v>155</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>358</v>
+      <c r="C173" s="19" t="s">
+        <v>357</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E173" s="6"/>
       <c r="F173" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I173" s="11">
-        <v>37987</v>
-      </c>
-      <c r="J173" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I173" s="10">
+        <v>38353</v>
+      </c>
+      <c r="J173" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K173" s="4"/>
+    </row>
+    <row r="174" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B174" s="6">
         <v>156</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>364</v>
+      <c r="C174" s="19" t="s">
+        <v>375</v>
       </c>
       <c r="E174" s="6"/>
       <c r="F174" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I174" s="11">
-        <v>38353</v>
-      </c>
-      <c r="J174" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I174" s="10">
+        <v>38718</v>
+      </c>
+      <c r="J174" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K174" s="4"/>
+    </row>
+    <row r="175" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B175" s="6">
         <v>157</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>377</v>
+      <c r="C175" s="19" t="s">
+        <v>336</v>
       </c>
       <c r="E175" s="6"/>
       <c r="F175" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H175" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I175" s="11">
-        <v>38718</v>
-      </c>
-      <c r="J175" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I175" s="10">
+        <v>42005</v>
+      </c>
+      <c r="J175" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K175" s="4"/>
+    </row>
+    <row r="176" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B176" s="6">
         <v>158</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>338</v>
+      <c r="C176" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="E176" s="6"/>
       <c r="F176" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I176" s="11">
-        <v>42005</v>
-      </c>
-      <c r="J176" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I176" s="10">
+        <v>44562</v>
+      </c>
+      <c r="J176" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K176" s="4"/>
+    </row>
+    <row r="177" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B177" s="6">
         <v>159</v>
       </c>
-      <c r="C177" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>368</v>
+      <c r="C177" s="19" t="s">
+        <v>374</v>
       </c>
       <c r="E177" s="6"/>
       <c r="F177" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I177" s="11">
-        <v>44562</v>
-      </c>
-      <c r="J177" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I177" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J177" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K177" s="4"/>
+    </row>
+    <row r="178" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B178" s="6">
         <v>160</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>376</v>
+      <c r="C178" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="E178" s="6"/>
       <c r="F178" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I178" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J178" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I178" s="10">
+        <v>37257</v>
+      </c>
+      <c r="J178" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K178" s="4"/>
+    </row>
+    <row r="179" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B179" s="6">
         <v>161</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>374</v>
+      <c r="C179" s="19" t="s">
+        <v>373</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="E179" s="6"/>
       <c r="F179" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H179" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I179" s="11">
+        <v>386</v>
+      </c>
+      <c r="I179" s="10">
         <v>37257</v>
       </c>
-      <c r="J179" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J179" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K179" s="4"/>
+    </row>
+    <row r="180" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B180" s="6">
         <v>162</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>375</v>
+      <c r="C180" s="19" t="s">
+        <v>332</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="E180" s="6"/>
       <c r="F180" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I180" s="11">
-        <v>37257</v>
-      </c>
-      <c r="J180" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I180" s="10">
+        <v>39083</v>
+      </c>
+      <c r="J180" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K180" s="4"/>
+    </row>
+    <row r="181" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B181" s="6">
         <v>163</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>350</v>
+      <c r="C181" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="E181" s="6"/>
       <c r="F181" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I181" s="11">
-        <v>39083</v>
-      </c>
-      <c r="J181" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I181" s="10">
+        <v>39448</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K181" s="4"/>
+    </row>
+    <row r="182" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B182" s="6">
         <v>164</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>373</v>
+      <c r="C182" s="19" t="s">
+        <v>370</v>
       </c>
       <c r="E182" s="6"/>
       <c r="F182" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I182" s="11">
-        <v>39448</v>
-      </c>
-      <c r="J182" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I182" s="10">
+        <v>42005</v>
+      </c>
+      <c r="J182" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K182" s="4"/>
+    </row>
+    <row r="183" spans="2:11" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B183" s="6">
         <v>165</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>372</v>
+      <c r="C183" s="19" t="s">
+        <v>379</v>
       </c>
       <c r="E183" s="6"/>
       <c r="F183" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H183" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I183" s="11">
-        <v>42005</v>
-      </c>
-      <c r="J183" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I183" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K183" s="4"/>
+    </row>
+    <row r="184" spans="2:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B184" s="6">
         <v>166</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>381</v>
+      <c r="C184" s="19" t="s">
+        <v>380</v>
       </c>
       <c r="E184" s="6"/>
       <c r="F184" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I184" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J184" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I184" s="10">
+        <v>44562</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K184" s="4"/>
+    </row>
+    <row r="185" spans="2:11" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B185" s="6">
         <v>167</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>382</v>
+      <c r="C185" s="19" t="s">
+        <v>342</v>
       </c>
       <c r="E185" s="6"/>
       <c r="F185" s="6" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H185" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I185" s="11">
-        <v>44562</v>
-      </c>
-      <c r="J185" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="I185" s="10">
+        <v>44197</v>
+      </c>
+      <c r="J185" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K185" s="4"/>
+    </row>
+    <row r="186" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B186" s="6">
         <v>168</v>
       </c>
-      <c r="C186" s="1" t="s">
-        <v>344</v>
+      <c r="C186" s="19" t="s">
+        <v>343</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I186" s="11">
+        <v>386</v>
+      </c>
+      <c r="I186" s="10">
         <v>44197</v>
       </c>
-      <c r="J186" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J186" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K186" s="4"/>
+    </row>
+    <row r="187" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B187" s="6">
         <v>169</v>
       </c>
-      <c r="C187" s="1" t="s">
-        <v>345</v>
+      <c r="C187" s="19" t="s">
+        <v>344</v>
       </c>
       <c r="E187" s="6"/>
       <c r="F187" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H187" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I187" s="11">
+        <v>386</v>
+      </c>
+      <c r="I187" s="10">
         <v>44197</v>
       </c>
-      <c r="J187" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J187" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K187" s="4"/>
+    </row>
+    <row r="188" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B188" s="6">
         <v>170</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>346</v>
+      <c r="C188" s="19" t="s">
+        <v>345</v>
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I188" s="11">
+        <v>386</v>
+      </c>
+      <c r="I188" s="10">
         <v>44197</v>
       </c>
-      <c r="J188" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J188" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K188" s="4"/>
+    </row>
+    <row r="189" spans="2:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B189" s="6">
         <v>171</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>347</v>
+      <c r="C189" s="19" t="s">
+        <v>346</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I189" s="11">
+        <v>386</v>
+      </c>
+      <c r="I189" s="10">
         <v>44197</v>
       </c>
-      <c r="J189" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J189" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="K189" s="4"/>
+    </row>
+    <row r="190" spans="2:11" ht="138" x14ac:dyDescent="0.25">
       <c r="B190" s="6">
         <v>172</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E190" s="6"/>
+      <c r="C190" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="E190" s="7"/>
       <c r="F190" s="6" t="s">
-        <v>398</v>
+        <v>197</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H190" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="I190" s="11">
-        <v>44197</v>
-      </c>
-      <c r="J190" s="10" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="191" spans="2:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="H190" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I190" s="10">
+        <v>45549</v>
+      </c>
+      <c r="J190" s="9"/>
+      <c r="K190" s="4"/>
+    </row>
+    <row r="191" spans="2:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B191" s="6">
         <v>173</v>
       </c>
@@ -7989,49 +8196,53 @@
       <c r="D191" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E191" s="7"/>
-      <c r="F191" s="6" t="s">
-        <v>197</v>
+      <c r="E191" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H191" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I191" s="11">
-        <v>45549</v>
-      </c>
-      <c r="J191" s="10"/>
-    </row>
-    <row r="192" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="I191" s="13">
+        <v>42298</v>
+      </c>
+      <c r="J191" s="9"/>
+      <c r="K191" s="4"/>
+    </row>
+    <row r="192" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B192" s="6">
         <v>174</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="E192" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F192" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>10</v>
+        <v>411</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G192" s="18" t="s">
+        <v>571</v>
       </c>
       <c r="H192" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="I192" s="14">
-        <v>42298</v>
-      </c>
-      <c r="J192" s="10"/>
-    </row>
-    <row r="193" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I192" s="13">
+        <v>45687</v>
+      </c>
+      <c r="J192" s="9"/>
+      <c r="K192" s="4"/>
+    </row>
+    <row r="193" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B193" s="6">
         <v>175</v>
       </c>
@@ -8041,109 +8252,111 @@
       <c r="D193" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="E193" s="7" t="s">
-        <v>588</v>
-      </c>
+      <c r="E193" s="7"/>
       <c r="F193" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G193" s="23" t="s">
-        <v>579</v>
+      <c r="G193" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I193" s="14">
-        <v>45687</v>
-      </c>
-      <c r="J193" s="10"/>
-    </row>
-    <row r="194" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I193" s="13">
+        <v>45623</v>
+      </c>
+      <c r="J193" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="K193" s="4"/>
+    </row>
+    <row r="194" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B194" s="6">
         <v>176</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E194" s="7"/>
-      <c r="F194" s="6" t="s">
-        <v>197</v>
+        <v>608</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G194" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H194" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I194" s="14">
-        <v>45623</v>
-      </c>
-      <c r="J194" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="H194" s="6"/>
+      <c r="I194" s="13">
+        <v>45709</v>
+      </c>
+      <c r="J194" s="9"/>
+      <c r="K194" s="4"/>
+    </row>
+    <row r="195" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B195" s="6">
         <v>177</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="E195" s="7" t="s">
-        <v>582</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="E195" s="7"/>
       <c r="F195" s="7" t="s">
         <v>110</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H195" s="6"/>
-      <c r="I195" s="14">
-        <v>45709</v>
-      </c>
-      <c r="J195" s="10"/>
-    </row>
-    <row r="196" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="H195" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="I195" s="13">
+        <v>45699</v>
+      </c>
+      <c r="J195" s="9"/>
+      <c r="K195" s="4"/>
+    </row>
+    <row r="196" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B196" s="6">
         <v>178</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>418</v>
       </c>
       <c r="E196" s="7"/>
-      <c r="F196" s="7" t="s">
-        <v>110</v>
+      <c r="F196" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H196" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I196" s="14">
-        <v>45699</v>
-      </c>
-      <c r="J196" s="10"/>
-    </row>
-    <row r="197" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I196" s="13">
+        <v>45645</v>
+      </c>
+      <c r="J196" s="9"/>
+      <c r="K196" s="4"/>
+    </row>
+    <row r="197" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B197" s="6">
         <v>179</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E197" s="7"/>
       <c r="F197" s="6" t="s">
@@ -8153,22 +8366,21 @@
         <v>10</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I197" s="14">
-        <v>45645</v>
-      </c>
-      <c r="J197" s="10"/>
-    </row>
-    <row r="198" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="I197" s="14"/>
+      <c r="J197" s="9"/>
+      <c r="K197" s="4"/>
+    </row>
+    <row r="198" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B198" s="6">
         <v>180</v>
       </c>
       <c r="C198" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D198" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="D198" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="E198" s="7"/>
       <c r="F198" s="6" t="s">
@@ -8178,76 +8390,83 @@
         <v>10</v>
       </c>
       <c r="H198" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I198" s="15"/>
-      <c r="J198" s="10"/>
-    </row>
-    <row r="199" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I198" s="13">
+        <v>45671</v>
+      </c>
+      <c r="J198" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="K198" s="21">
+        <v>45723</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B199" s="6">
         <v>181</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="E199" s="7"/>
-      <c r="F199" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+        <v>425</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G199" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="H199" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I199" s="14">
-        <v>45671</v>
+        <v>66</v>
+      </c>
+      <c r="I199" s="13">
+        <v>45743</v>
       </c>
       <c r="J199" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="K199" s="4"/>
+    </row>
+    <row r="200" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B200" s="6">
         <v>182</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="D200" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E200" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="F200" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G200" s="21" t="s">
-        <v>43</v>
+        <v>447</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="E200" s="7"/>
+      <c r="F200" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H200" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I200" s="14">
-        <v>45743</v>
-      </c>
-      <c r="J200" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="I200" s="13">
+        <v>45838</v>
+      </c>
+      <c r="J200" s="9"/>
+      <c r="K200" s="4"/>
+    </row>
+    <row r="201" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B201" s="6">
         <v>183</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>454</v>
+        <v>448</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="E201" s="7"/>
       <c r="F201" s="6" t="s">
@@ -8259,12 +8478,13 @@
       <c r="H201" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I201" s="14">
-        <v>45838</v>
-      </c>
-      <c r="J201" s="10"/>
-    </row>
-    <row r="202" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I201" s="13">
+        <v>45840</v>
+      </c>
+      <c r="J201" s="9"/>
+      <c r="K201" s="4"/>
+    </row>
+    <row r="202" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B202" s="6">
         <v>184</v>
       </c>
@@ -8272,11 +8492,13 @@
         <v>452</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="E202" s="7"/>
-      <c r="F202" s="6" t="s">
-        <v>197</v>
+        <v>451</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>10</v>
@@ -8284,125 +8506,133 @@
       <c r="H202" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I202" s="14">
-        <v>45840</v>
-      </c>
-      <c r="J202" s="10"/>
-    </row>
-    <row r="203" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I202" s="13">
+        <v>45826</v>
+      </c>
+      <c r="J202" s="9"/>
+      <c r="K202" s="4"/>
+    </row>
+    <row r="203" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B203" s="6">
         <v>185</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>455</v>
+        <v>610</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="F203" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="F203" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H203" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="I203" s="14">
-        <v>45826</v>
-      </c>
-      <c r="J203" s="10"/>
-    </row>
-    <row r="204" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="H203" s="7"/>
+      <c r="I203" s="13">
+        <v>45938</v>
+      </c>
+      <c r="J203" s="9"/>
+      <c r="K203" s="4"/>
+    </row>
+    <row r="204" spans="1:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B204" s="6">
         <v>186</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>457</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H204" s="7"/>
-      <c r="I204" s="14">
-        <v>45938</v>
-      </c>
-      <c r="J204" s="10"/>
-    </row>
-    <row r="205" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="I204" s="13">
+        <v>45951</v>
+      </c>
+      <c r="J204" s="9"/>
+      <c r="K204" s="4"/>
+    </row>
+    <row r="205" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B205" s="6">
         <v>187</v>
       </c>
-      <c r="C205" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="D205" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>463</v>
+      <c r="C205" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>515</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H205" s="7"/>
-      <c r="I205" s="14">
-        <v>45951</v>
-      </c>
-      <c r="J205" s="10"/>
-    </row>
-    <row r="206" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="H205" s="6"/>
+      <c r="I205" s="10">
+        <v>45952</v>
+      </c>
+      <c r="J205" s="9"/>
+      <c r="K205" s="4"/>
+    </row>
+    <row r="206" spans="1:11" ht="234.6" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>611</v>
+      </c>
       <c r="B206" s="6">
         <v>188</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>464</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>110</v>
+        <v>465</v>
+      </c>
+      <c r="F206" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G206" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H206" s="7"/>
-      <c r="I206" s="14">
-        <v>45952</v>
-      </c>
-      <c r="J206" s="10"/>
-    </row>
-    <row r="207" spans="2:10" ht="234.6" x14ac:dyDescent="0.25">
+      <c r="I206" s="10">
+        <v>45994</v>
+      </c>
+      <c r="J206" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="K206" s="4"/>
+    </row>
+    <row r="207" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B207" s="6">
         <v>189</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C207" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="E207" s="7" t="s">
         <v>468</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="E207" s="6" t="s">
-        <v>470</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>197</v>
@@ -8410,26 +8640,25 @@
       <c r="G207" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H207" s="6"/>
-      <c r="I207" s="11">
-        <v>45994</v>
-      </c>
-      <c r="J207" s="6" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="208" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="H207" s="7"/>
+      <c r="I207" s="10">
+        <v>45999</v>
+      </c>
+      <c r="J207" s="9"/>
+      <c r="K207" s="4"/>
+    </row>
+    <row r="208" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B208" s="6">
         <v>190</v>
       </c>
       <c r="C208" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E208" s="7" t="s">
         <v>471</v>
-      </c>
-      <c r="D208" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E208" s="7" t="s">
-        <v>473</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>197</v>
@@ -8438,37 +8667,39 @@
         <v>10</v>
       </c>
       <c r="H208" s="7"/>
-      <c r="I208" s="11">
+      <c r="I208" s="10">
         <v>45999</v>
       </c>
-      <c r="J208" s="10"/>
-    </row>
-    <row r="209" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="J208" s="9"/>
+      <c r="K208" s="4"/>
+    </row>
+    <row r="209" spans="1:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B209" s="6">
         <v>191</v>
       </c>
       <c r="C209" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E209" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="D209" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="E209" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="F209" s="6" t="s">
+      <c r="F209" s="7" t="s">
         <v>197</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H209" s="7"/>
-      <c r="I209" s="11">
-        <v>45999</v>
-      </c>
-      <c r="J209" s="10"/>
-    </row>
-    <row r="210" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
+      <c r="I209" s="13">
+        <v>46008</v>
+      </c>
+      <c r="J209" s="9"/>
+      <c r="K209" s="4"/>
+    </row>
+    <row r="210" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="B210" s="6">
         <v>192</v>
       </c>
@@ -8476,32 +8707,36 @@
         <v>477</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="F210" s="6" t="s">
-        <v>197</v>
+        <v>475</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="G210" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H210" s="7"/>
-      <c r="I210" s="11">
-        <v>46008</v>
-      </c>
-      <c r="J210" s="10"/>
-    </row>
-    <row r="211" spans="2:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="I210" s="13">
+        <v>45966</v>
+      </c>
+      <c r="J210" s="9"/>
+      <c r="K210" s="4"/>
+    </row>
+    <row r="211" spans="1:11" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="B211" s="6">
         <v>193</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>480</v>
@@ -8509,230 +8744,241 @@
       <c r="F211" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="G211" s="3" t="s">
+      <c r="G211" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H211" s="7"/>
-      <c r="I211" s="14">
-        <v>45966</v>
-      </c>
-      <c r="J211" s="10"/>
-    </row>
-    <row r="212" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I211" s="13">
+        <v>45994</v>
+      </c>
+      <c r="J211" s="14"/>
+      <c r="K211" s="4"/>
+    </row>
+    <row r="212" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B212" s="6">
         <v>194</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D212" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="E212" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="E212" s="7" t="s">
-        <v>485</v>
-      </c>
       <c r="F212" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G212" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G212" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H212" s="7"/>
-      <c r="I212" s="14">
-        <v>45994</v>
-      </c>
-      <c r="J212" s="10"/>
-    </row>
-    <row r="213" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I212" s="13">
+        <v>43006</v>
+      </c>
+      <c r="J212" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K212" s="4"/>
+    </row>
+    <row r="213" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B213" s="6">
         <v>195</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G213" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="G213" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H213" s="7"/>
-      <c r="I213" s="14">
-        <v>43006</v>
-      </c>
-      <c r="J213" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="214" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I213" s="13">
+        <v>43262</v>
+      </c>
+      <c r="J213" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K213" s="4"/>
+    </row>
+    <row r="214" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B214" s="6">
         <v>196</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G214" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="G214" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H214" s="7"/>
-      <c r="I214" s="14">
-        <v>43262</v>
-      </c>
-      <c r="J214" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="215" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I214" s="13">
+        <v>44335</v>
+      </c>
+      <c r="J214" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K214" s="4"/>
+    </row>
+    <row r="215" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B215" s="6">
         <v>197</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G215" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="G215" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H215" s="7"/>
-      <c r="I215" s="14">
-        <v>44335</v>
-      </c>
-      <c r="J215" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="216" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I215" s="13">
+        <v>44212</v>
+      </c>
+      <c r="J215" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K215" s="4"/>
+    </row>
+    <row r="216" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B216" s="6">
         <v>198</v>
       </c>
       <c r="C216" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="F216" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D216" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="E216" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F216" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G216" s="19" t="s">
+      <c r="G216" s="15" t="s">
         <v>10</v>
       </c>
       <c r="H216" s="7"/>
-      <c r="I216" s="14">
-        <v>44212</v>
-      </c>
-      <c r="J216" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="217" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I216" s="13">
+        <v>44785</v>
+      </c>
+      <c r="J216" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K216" s="4"/>
+    </row>
+    <row r="217" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B217" s="6">
         <v>199</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D217" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="E217" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="G217" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H217" s="7"/>
+      <c r="I217" s="13">
+        <v>43648</v>
+      </c>
+      <c r="J217" s="14" t="s">
         <v>503</v>
       </c>
-      <c r="E217" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="F217" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G217" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H217" s="7"/>
-      <c r="I217" s="14">
-        <v>44785</v>
-      </c>
-      <c r="J217" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="218" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="K217" s="4"/>
+    </row>
+    <row r="218" spans="1:11" ht="41.4" x14ac:dyDescent="0.25">
       <c r="B218" s="6">
         <v>200</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G218" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="G218" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H218" s="7"/>
-      <c r="I218" s="14">
-        <v>43648</v>
-      </c>
-      <c r="J218" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="219" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="I218" s="13">
+        <v>45894</v>
+      </c>
+      <c r="J218" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="K218" s="4"/>
+    </row>
+    <row r="219" spans="1:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B219" s="6">
         <v>201</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G219" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G219" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H219" s="7"/>
-      <c r="I219" s="14">
-        <v>45894</v>
-      </c>
-      <c r="J219" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="220" spans="2:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="I219" s="13">
+        <v>45471</v>
+      </c>
+      <c r="J219" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K219" s="4"/>
+    </row>
+    <row r="220" spans="1:11" ht="138" x14ac:dyDescent="0.25">
       <c r="B220" s="6">
         <v>202</v>
       </c>
@@ -8743,7 +8989,7 @@
         <v>512</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>110</v>
@@ -8752,25 +8998,26 @@
         <v>10</v>
       </c>
       <c r="H220" s="7"/>
-      <c r="I220" s="14">
-        <v>45471</v>
-      </c>
-      <c r="J220" s="15" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="221" spans="2:10" ht="138" x14ac:dyDescent="0.25">
+      <c r="I220" s="13">
+        <v>46022</v>
+      </c>
+      <c r="J220" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="K220" s="4"/>
+    </row>
+    <row r="221" spans="1:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B221" s="6">
         <v>203</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D221" s="7" t="s">
         <v>517</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F221" s="7" t="s">
         <v>110</v>
@@ -8779,25 +9026,24 @@
         <v>10</v>
       </c>
       <c r="H221" s="7"/>
-      <c r="I221" s="14">
-        <v>46022</v>
-      </c>
-      <c r="J221" s="15" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="222" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I221" s="13">
+        <v>46008</v>
+      </c>
+      <c r="J221" s="14"/>
+      <c r="K221" s="4"/>
+    </row>
+    <row r="222" spans="1:11" ht="207" x14ac:dyDescent="0.25">
       <c r="B222" s="6">
         <v>204</v>
       </c>
       <c r="C222" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="E222" s="7" t="s">
         <v>521</v>
-      </c>
-      <c r="D222" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="E222" s="7" t="s">
-        <v>523</v>
       </c>
       <c r="F222" s="7" t="s">
         <v>110</v>
@@ -8806,95 +9052,97 @@
         <v>10</v>
       </c>
       <c r="H222" s="7"/>
-      <c r="I222" s="14">
-        <v>46008</v>
-      </c>
-      <c r="J222" s="15"/>
-    </row>
-    <row r="223" spans="2:10" ht="207" x14ac:dyDescent="0.25">
+      <c r="I222" s="13">
+        <v>45974</v>
+      </c>
+      <c r="J222" s="14"/>
+      <c r="K222" s="4"/>
+    </row>
+    <row r="223" spans="1:11" ht="234.6" x14ac:dyDescent="0.25">
       <c r="B223" s="6">
         <v>205</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D223" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E223" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="E223" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="F223" s="7" t="s">
+      <c r="F223" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H223" s="7"/>
-      <c r="I223" s="14">
-        <v>45974</v>
-      </c>
-      <c r="J223" s="15"/>
-    </row>
-    <row r="224" spans="2:10" ht="234.6" x14ac:dyDescent="0.25">
+      <c r="I223" s="13">
+        <v>45987</v>
+      </c>
+      <c r="J223" s="14"/>
+      <c r="K223" s="4"/>
+    </row>
+    <row r="224" spans="1:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="B224" s="6">
         <v>206</v>
       </c>
       <c r="C224" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E224" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="D224" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="E224" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="F224" s="7" t="s">
+      <c r="F224" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H224" s="7"/>
-      <c r="I224" s="14">
+      <c r="I224" s="13">
         <v>45987</v>
       </c>
-      <c r="J224" s="15"/>
-    </row>
-    <row r="225" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="J224" s="14"/>
+      <c r="K224" s="4"/>
+    </row>
+    <row r="225" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B225" s="6">
         <v>207</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D225" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="E225" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>110</v>
+      <c r="E225" s="7"/>
+      <c r="F225" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H225" s="7"/>
-      <c r="I225" s="14">
-        <v>45987</v>
-      </c>
-      <c r="J225" s="15"/>
-    </row>
-    <row r="226" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I225" s="13">
+        <v>45798</v>
+      </c>
+      <c r="J225" s="14"/>
+      <c r="K225" s="4"/>
+    </row>
+    <row r="226" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
       <c r="B226" s="6">
         <v>208</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" s="6" t="s">
@@ -8904,17 +9152,18 @@
         <v>10</v>
       </c>
       <c r="H226" s="7"/>
-      <c r="I226" s="14">
-        <v>45798</v>
-      </c>
-      <c r="J226" s="15"/>
-    </row>
-    <row r="227" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="I226" s="13">
+        <v>45849</v>
+      </c>
+      <c r="J226" s="14"/>
+      <c r="K226" s="4"/>
+    </row>
+    <row r="227" spans="2:11" ht="179.4" x14ac:dyDescent="0.25">
       <c r="B227" s="6">
         <v>209</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D227" s="7" t="s">
         <v>535</v>
@@ -8927,20 +9176,21 @@
         <v>10</v>
       </c>
       <c r="H227" s="7"/>
-      <c r="I227" s="14">
+      <c r="I227" s="13">
         <v>45849</v>
       </c>
-      <c r="J227" s="15"/>
-    </row>
-    <row r="228" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="J227" s="14"/>
+      <c r="K227" s="4"/>
+    </row>
+    <row r="228" spans="2:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B228" s="6">
         <v>210</v>
       </c>
       <c r="C228" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="D228" s="7" t="s">
         <v>537</v>
-      </c>
-      <c r="D228" s="7" t="s">
-        <v>540</v>
       </c>
       <c r="E228" s="7"/>
       <c r="F228" s="6" t="s">
@@ -8950,22 +9200,25 @@
         <v>10</v>
       </c>
       <c r="H228" s="7"/>
-      <c r="I228" s="14">
-        <v>45849</v>
-      </c>
-      <c r="J228" s="15"/>
-    </row>
-    <row r="229" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="B229" s="7">
+      <c r="I228" s="13">
+        <v>46043</v>
+      </c>
+      <c r="J228" s="14"/>
+      <c r="K228" s="4"/>
+    </row>
+    <row r="229" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="B229" s="6">
         <v>211</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E229" s="7"/>
+        <v>539</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>581</v>
+      </c>
       <c r="F229" s="6" t="s">
         <v>197</v>
       </c>
@@ -8973,24 +9226,23 @@
         <v>10</v>
       </c>
       <c r="H229" s="7"/>
-      <c r="I229" s="14">
-        <v>46043</v>
-      </c>
-      <c r="J229" s="15"/>
-    </row>
-    <row r="230" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="I229" s="13">
+        <v>46052</v>
+      </c>
+      <c r="J229" s="14"/>
+      <c r="K229" s="4"/>
+    </row>
+    <row r="230" spans="2:11" ht="82.8" x14ac:dyDescent="0.25">
       <c r="B230" s="6">
         <v>212</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="E230" s="7" t="s">
-        <v>589</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="E230" s="7"/>
       <c r="F230" s="6" t="s">
         <v>197</v>
       </c>
@@ -8998,46 +9250,50 @@
         <v>10</v>
       </c>
       <c r="H230" s="7"/>
-      <c r="I230" s="14">
-        <v>46052</v>
-      </c>
-      <c r="J230" s="15"/>
-    </row>
-    <row r="231" spans="2:10" ht="82.8" x14ac:dyDescent="0.25">
+      <c r="I230" s="13">
+        <v>46071</v>
+      </c>
+      <c r="J230" s="14"/>
+      <c r="K230" s="4"/>
+    </row>
+    <row r="231" spans="2:11" ht="124.2" x14ac:dyDescent="0.25">
       <c r="B231" s="6">
         <v>213</v>
       </c>
       <c r="C231" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H231" s="7"/>
+      <c r="I231" s="13">
+        <v>46071</v>
+      </c>
+      <c r="J231" s="14"/>
+      <c r="K231" s="4"/>
+    </row>
+    <row r="232" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B232" s="6">
+        <v>214</v>
+      </c>
+      <c r="C232" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="D231" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="E231" s="7"/>
-      <c r="F231" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H231" s="7"/>
-      <c r="I231" s="14">
-        <v>46071</v>
-      </c>
-      <c r="J231" s="15"/>
-    </row>
-    <row r="232" spans="2:10" ht="124.2" x14ac:dyDescent="0.25">
-      <c r="B232" s="7">
-        <v>214</v>
-      </c>
-      <c r="C232" s="7" t="s">
+      <c r="D232" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="E232" s="7" t="s">
         <v>546</v>
-      </c>
-      <c r="D232" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="E232" s="7" t="s">
-        <v>558</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>197</v>
@@ -9046,72 +9302,79 @@
         <v>10</v>
       </c>
       <c r="H232" s="7"/>
-      <c r="I232" s="14">
-        <v>46071</v>
-      </c>
-      <c r="J232" s="15"/>
-    </row>
-    <row r="233" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="I232" s="13">
+        <v>46076</v>
+      </c>
+      <c r="J232" s="14"/>
+      <c r="K232" s="4"/>
+    </row>
+    <row r="233" spans="2:11" ht="193.2" x14ac:dyDescent="0.25">
       <c r="B233" s="6">
         <v>215</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H233" s="7"/>
-      <c r="I233" s="14">
-        <v>46076</v>
-      </c>
-      <c r="J233" s="15"/>
-    </row>
-    <row r="234" spans="2:10" ht="193.2" x14ac:dyDescent="0.25">
+      <c r="I233" s="13">
+        <v>45681</v>
+      </c>
+      <c r="J233" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="K233" s="4"/>
+    </row>
+    <row r="234" spans="2:11" ht="69" x14ac:dyDescent="0.25">
       <c r="B234" s="6">
         <v>216</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D234" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E234" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="E234" s="7" t="s">
-        <v>553</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>110</v>
+      <c r="F234" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H234" s="7"/>
-      <c r="I234" s="14">
-        <v>45681</v>
-      </c>
-      <c r="J234" s="15" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="235" spans="2:10" ht="69" x14ac:dyDescent="0.25">
-      <c r="B235" s="7">
+      <c r="I234" s="13">
+        <v>46050</v>
+      </c>
+      <c r="J234" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="K234" s="21">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="235" spans="2:11" ht="276" x14ac:dyDescent="0.25">
+      <c r="B235" s="6">
         <v>217</v>
       </c>
       <c r="C235" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="D235" s="7" t="s">
         <v>555</v>
-      </c>
-      <c r="D235" s="7" t="s">
-        <v>556</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>557</v>
@@ -9123,25 +9386,26 @@
         <v>10</v>
       </c>
       <c r="H235" s="7"/>
-      <c r="I235" s="14">
-        <v>46050</v>
-      </c>
-      <c r="J235" s="15" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="236" spans="2:10" ht="276" x14ac:dyDescent="0.25">
-      <c r="B236" s="7">
+      <c r="I235" s="13">
+        <v>46008</v>
+      </c>
+      <c r="J235" s="14"/>
+      <c r="K235" s="21">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="236" spans="2:11" ht="138" x14ac:dyDescent="0.25">
+      <c r="B236" s="6">
         <v>218</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="F236" s="6" t="s">
         <v>197</v>
@@ -9150,23 +9414,24 @@
         <v>10</v>
       </c>
       <c r="H236" s="7"/>
-      <c r="I236" s="14">
-        <v>46008</v>
-      </c>
-      <c r="J236" s="15"/>
-    </row>
-    <row r="237" spans="2:10" ht="138" x14ac:dyDescent="0.25">
-      <c r="B237" s="7">
+      <c r="I236" s="13">
+        <v>45874</v>
+      </c>
+      <c r="J236" s="14"/>
+      <c r="K236" s="4"/>
+    </row>
+    <row r="237" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B237" s="6">
         <v>219</v>
       </c>
-      <c r="C237" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="D237" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="E237" s="7" t="s">
-        <v>591</v>
+      <c r="C237" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="D237" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>560</v>
       </c>
       <c r="F237" s="6" t="s">
         <v>197</v>
@@ -9174,100 +9439,108 @@
       <c r="G237" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H237" s="7"/>
-      <c r="I237" s="14">
-        <v>45874</v>
-      </c>
-      <c r="J237" s="15"/>
-    </row>
-    <row r="238" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="B238" s="7">
+      <c r="H237" s="6"/>
+      <c r="I237" s="10">
+        <v>46010</v>
+      </c>
+      <c r="J237" s="9"/>
+      <c r="K237" s="21">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="238" spans="2:11" ht="96.6" x14ac:dyDescent="0.25">
+      <c r="B238" s="6">
         <v>220</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="F238" s="6" t="s">
+      <c r="F238" s="7" t="s">
         <v>197</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H238" s="7"/>
-      <c r="I238" s="14">
-        <v>46010</v>
-      </c>
-      <c r="J238" s="15"/>
-    </row>
-    <row r="239" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="B239" s="7">
+      <c r="I238" s="13">
+        <v>46128</v>
+      </c>
+      <c r="J238" s="14"/>
+      <c r="K238" s="4"/>
+    </row>
+    <row r="239" spans="2:11" ht="69" x14ac:dyDescent="0.25">
+      <c r="B239" s="6">
         <v>221</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D239" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="E239" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="E239" s="7" t="s">
-        <v>570</v>
-      </c>
       <c r="F239" s="7" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H239" s="7"/>
-      <c r="I239" s="14">
-        <v>45826</v>
-      </c>
-      <c r="J239" s="15"/>
-    </row>
-    <row r="240" spans="2:10" ht="96.6" x14ac:dyDescent="0.25">
-      <c r="B240" s="7">
+      <c r="I239" s="13">
+        <v>46086</v>
+      </c>
+      <c r="J239" s="14"/>
+      <c r="K239" s="21">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="240" spans="2:11" ht="207" x14ac:dyDescent="0.25">
+      <c r="B240" s="6">
         <v>222</v>
       </c>
-      <c r="C240" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="D240" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="E240" s="7" t="s">
-        <v>573</v>
+      <c r="C240" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="D240" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>587</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>197</v>
+        <v>493</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H240" s="7"/>
-      <c r="I240" s="14">
-        <v>46128</v>
-      </c>
-      <c r="J240" s="15"/>
-    </row>
-    <row r="241" spans="2:10" ht="69" x14ac:dyDescent="0.25">
+      <c r="H240" s="6"/>
+      <c r="I240" s="10">
+        <v>45457</v>
+      </c>
+      <c r="J240" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="K240" s="4"/>
+    </row>
+    <row r="241" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
       <c r="B241" s="6">
         <v>223</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="E241" s="6" t="s">
-        <v>576</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="E241" s="6"/>
       <c r="F241" s="6" t="s">
         <v>197</v>
       </c>
@@ -9275,163 +9548,158 @@
         <v>10</v>
       </c>
       <c r="H241" s="6"/>
-      <c r="I241" s="11">
-        <v>46086</v>
-      </c>
-      <c r="J241" s="10"/>
-    </row>
-    <row r="242" spans="2:10" ht="207" x14ac:dyDescent="0.25">
-      <c r="B242" s="7">
+      <c r="I241" s="10">
+        <v>45483</v>
+      </c>
+      <c r="J241" s="9"/>
+      <c r="K241" s="4"/>
+    </row>
+    <row r="242" spans="2:11" ht="179.4" x14ac:dyDescent="0.25">
+      <c r="B242" s="6">
         <v>224</v>
       </c>
-      <c r="C242" s="7" t="s">
+      <c r="C242" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H242" s="6"/>
+      <c r="I242" s="10">
+        <v>46175</v>
+      </c>
+      <c r="J242" s="9"/>
+      <c r="K242" s="21">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="243" spans="2:11" ht="248.4" x14ac:dyDescent="0.25">
+      <c r="B243" s="6">
+        <v>225</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="D243" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="F243" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H243" s="6"/>
+      <c r="I243" s="10">
+        <v>46181</v>
+      </c>
+      <c r="J243" s="9"/>
+      <c r="K243" s="21">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="244" spans="2:11" ht="151.80000000000001" x14ac:dyDescent="0.25">
+      <c r="B244" s="6">
+        <v>226</v>
+      </c>
+      <c r="C244" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="D242" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="E242" s="7" t="s">
+      <c r="D244" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="F242" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H242" s="7"/>
-      <c r="I242" s="14">
-        <v>45457</v>
-      </c>
-      <c r="J242" s="15" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="243" spans="2:10" ht="110.4" x14ac:dyDescent="0.25">
-      <c r="B243" s="7">
-        <v>225</v>
-      </c>
-      <c r="C243" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="D243" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7" t="s">
+      <c r="E244" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="F244" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G243" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H243" s="7"/>
-      <c r="I243" s="14">
-        <v>45483</v>
-      </c>
-      <c r="J243" s="15"/>
-    </row>
-    <row r="244" spans="2:10" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="B244" s="24">
-        <v>226</v>
-      </c>
-      <c r="C244" s="24" t="s">
-        <v>599</v>
-      </c>
-      <c r="D244" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="E244" s="24"/>
-      <c r="F244" s="24" t="s">
+      <c r="G244" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H244" s="6"/>
+      <c r="I244" s="10">
+        <v>46177</v>
+      </c>
+      <c r="J244" s="9"/>
+      <c r="K244" s="10">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="245" spans="2:11" ht="207" x14ac:dyDescent="0.25">
+      <c r="B245" s="6">
+        <v>227</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="F245" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H245" s="7"/>
+      <c r="I245" s="13">
+        <v>45324</v>
+      </c>
+      <c r="J245" s="14"/>
+      <c r="K245" s="4"/>
+    </row>
+    <row r="246" spans="2:11" ht="110.4" x14ac:dyDescent="0.25">
+      <c r="B246" s="7">
+        <v>228</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="F246" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G244" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H244" s="24"/>
-      <c r="I244" s="25">
-        <v>45467</v>
-      </c>
-    </row>
-    <row r="245" spans="2:10" ht="179.4" x14ac:dyDescent="0.25">
-      <c r="B245" s="24">
-        <v>227</v>
-      </c>
-      <c r="C245" s="24" t="s">
-        <v>608</v>
-      </c>
-      <c r="D245" s="24" t="s">
-        <v>607</v>
-      </c>
-      <c r="E245" s="24" t="s">
-        <v>601</v>
-      </c>
-      <c r="F245" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="G245" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H245" s="24"/>
-      <c r="I245" s="25">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="246" spans="2:10" ht="248.4" x14ac:dyDescent="0.25">
-      <c r="B246" s="24">
-        <v>228</v>
-      </c>
-      <c r="C246" s="24" t="s">
-        <v>602</v>
-      </c>
-      <c r="D246" s="24" t="s">
-        <v>603</v>
-      </c>
-      <c r="E246" s="24" t="s">
-        <v>609</v>
-      </c>
-      <c r="F246" s="24" t="s">
-        <v>197</v>
-      </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H246" s="24"/>
-      <c r="I246" s="25">
-        <v>46181</v>
-      </c>
-    </row>
-    <row r="247" spans="2:10" ht="151.80000000000001" x14ac:dyDescent="0.25">
-      <c r="B247" s="24">
-        <v>229</v>
-      </c>
-      <c r="C247" s="24" t="s">
-        <v>604</v>
-      </c>
-      <c r="D247" s="24" t="s">
-        <v>605</v>
-      </c>
-      <c r="E247" s="24" t="s">
-        <v>606</v>
-      </c>
-      <c r="F247" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="G247" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H247" s="24"/>
-      <c r="I247" s="25">
-        <v>46177</v>
+      <c r="H246" s="7"/>
+      <c r="I246" s="13">
+        <v>46217</v>
+      </c>
+      <c r="J246" s="14"/>
+      <c r="K246" s="21">
+        <v>46246</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G193:H197">
-    <sortCondition ref="G193:G197"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G192:H196">
+    <sortCondition ref="G192:G196"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="C2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G19:G247">
+  <conditionalFormatting sqref="G19:G246">
     <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"Невідомо"</formula>
     </cfRule>
@@ -9505,121 +9773,121 @@
         <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="16">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="22">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="E3" s="16"/>
+      <c r="D3" s="22" t="s">
+        <v>427</v>
+      </c>
+      <c r="E3" s="22"/>
       <c r="F3" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17">
+      <c r="H3" s="22"/>
+      <c r="I3" s="23">
         <v>43117</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="B4" s="16">
+    <row r="4" spans="2:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="B4" s="22">
         <v>2</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="E4" s="16"/>
+      <c r="C4" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="E4" s="22"/>
       <c r="F4" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17">
+      <c r="H4" s="22"/>
+      <c r="I4" s="23">
         <v>45674</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="16">
+    <row r="5" spans="2:9" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="B5" s="22">
         <v>3</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>466</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="E5" s="16"/>
+      <c r="C5" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="E5" s="22"/>
       <c r="F5" s="6" t="s">
         <v>110</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="17">
+      <c r="H5" s="22"/>
+      <c r="I5" s="23">
         <v>43446</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="16">
+    <row r="6" spans="2:9" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="22">
         <v>4</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23">
+        <v>42173</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="22">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" s="22"/>
+      <c r="F7" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17">
-        <v>42173</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B7" s="16">
-        <v>5</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>437</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="6" t="s">
-        <v>438</v>
-      </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17">
+      <c r="H7" s="22"/>
+      <c r="I7" s="23">
         <v>44440</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="16">
+      <c r="B8" s="22">
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -9638,12 +9906,12 @@
         <v>10</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>43350</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="69" x14ac:dyDescent="0.3">
-      <c r="B9" s="16">
+      <c r="B9" s="22">
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -9662,22 +9930,22 @@
         <v>10</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>42965</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="16">
+      <c r="B10" s="22">
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>65</v>
@@ -9686,7 +9954,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <v>46388</v>
       </c>
     </row>
